--- a/CI compiled.xlsx
+++ b/CI compiled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boyuan/Desktop/Harvard/Research/Energy Metabolism Atlas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3D8CC1-69B3-5A4E-A62F-BA10AA630E2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58678F0-042B-844D-AD95-0B0F6BF9D571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="22340" windowWidth="30240" windowHeight="18900" activeTab="4" xr2:uid="{C27F82BD-D1C2-DF4B-9AB6-A06FDDA3A96C}"/>
+    <workbookView xWindow="4080" yWindow="22360" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{C27F82BD-D1C2-DF4B-9AB6-A06FDDA3A96C}"/>
   </bookViews>
   <sheets>
     <sheet name="Fasted base " sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
     <sheet name="Refed TAGkinetics_portalAAs" sheetId="5" r:id="rId5"/>
     <sheet name="flux_size" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -429,7 +429,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="171" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -688,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="92">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -756,18 +756,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -782,13 +775,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
@@ -805,9 +792,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -832,18 +816,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -889,7 +865,7 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -904,17 +880,32 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2188,23 +2179,23 @@
         <v>47</v>
       </c>
       <c r="H1" s="1"/>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="78" t="s">
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="79" t="s">
+      <c r="Q1" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="80" t="s">
+      <c r="R1" s="70" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2231,29 +2222,29 @@
         <v>7.55</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="J2" s="43"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="87"/>
+      <c r="K2" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="N2" s="49" t="s">
+      <c r="N2" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="P2" s="71" t="s">
+      <c r="O2" s="91"/>
+      <c r="P2" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="Q2" s="72">
-        <f>K3</f>
+      <c r="Q2" s="62">
+        <f t="shared" ref="Q2:R4" si="0">K3</f>
         <v>28.875</v>
       </c>
-      <c r="R2" s="73">
-        <f>L3</f>
+      <c r="R2" s="63">
+        <f t="shared" si="0"/>
         <v>2.25</v>
       </c>
     </row>
@@ -2283,34 +2274,34 @@
       <c r="I3" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="J3" s="54">
+      <c r="J3" s="48">
         <v>39</v>
       </c>
-      <c r="K3" s="44">
+      <c r="K3" s="40">
         <f>J3/J5*K5</f>
         <v>28.875</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="33">
         <f>K3/K5*L5</f>
         <v>2.25</v>
       </c>
-      <c r="M3" s="35">
+      <c r="M3" s="32">
         <f>K3/K5*M5</f>
         <v>21</v>
       </c>
-      <c r="N3" s="50">
+      <c r="N3" s="45">
         <f>M3/M5*N5</f>
         <v>2.25</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="P3" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="Q3" s="36">
-        <f>K4</f>
+      <c r="Q3" s="33">
+        <f t="shared" si="0"/>
         <v>57.75</v>
       </c>
-      <c r="R3" s="50">
-        <f>L4</f>
+      <c r="R3" s="45">
+        <f t="shared" si="0"/>
         <v>4.5</v>
       </c>
     </row>
@@ -2340,34 +2331,34 @@
       <c r="I4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="54">
+      <c r="J4" s="48">
         <v>78</v>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="40">
         <f>J4/J5*K5</f>
         <v>57.75</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="33">
         <f>K4/K5*L5</f>
         <v>4.5</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="32">
         <f>K4/K5*M5</f>
         <v>42</v>
       </c>
-      <c r="N4" s="50">
+      <c r="N4" s="45">
         <f>M4/M5*N5</f>
         <v>4.5</v>
       </c>
-      <c r="P4" s="38" t="s">
+      <c r="P4" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="Q4" s="39">
-        <f>K5</f>
+      <c r="Q4" s="36">
+        <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="R4" s="74">
-        <f>L5</f>
+      <c r="R4" s="64">
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
     </row>
@@ -2397,30 +2388,30 @@
       <c r="I5" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="55">
+      <c r="J5" s="49">
         <v>104</v>
       </c>
-      <c r="K5" s="56">
+      <c r="K5" s="50">
         <f>77</f>
         <v>77</v>
       </c>
-      <c r="L5" s="57">
+      <c r="L5" s="51">
         <v>6</v>
       </c>
-      <c r="M5" s="55">
+      <c r="M5" s="49">
         <v>56</v>
       </c>
-      <c r="N5" s="58">
+      <c r="N5" s="52">
         <v>6</v>
       </c>
-      <c r="P5" s="71" t="s">
+      <c r="P5" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="Q5" s="72">
+      <c r="Q5" s="62">
         <f>SUM(Q2:Q4) * 1/3</f>
         <v>54.541666666666664</v>
       </c>
-      <c r="R5" s="73">
+      <c r="R5" s="63">
         <f>SQRT(R2^2 + R3^2 + R4^2 ) * 1/3</f>
         <v>2.6100766272276377</v>
       </c>
@@ -2448,31 +2439,31 @@
         <v>1.1499999999999999</v>
       </c>
       <c r="H6" s="2"/>
-      <c r="K6" s="52">
+      <c r="K6" s="46">
         <f>SUM(K3:K5)</f>
         <v>163.625</v>
       </c>
-      <c r="L6" s="52">
+      <c r="L6" s="46">
         <f>SQRT(L3^2 + L4^2 +L5^2)</f>
         <v>7.8302298816829126</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="47">
         <f>SUM(M3:M5)</f>
         <v>119</v>
       </c>
-      <c r="N6" s="52">
+      <c r="N6" s="46">
         <f>SQRT(N3^2 + N4^2 +N5^2)</f>
         <v>7.8302298816829126</v>
       </c>
-      <c r="P6" s="71" t="s">
+      <c r="P6" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="Q6" s="75">
-        <f>M3</f>
+      <c r="Q6" s="65">
+        <f t="shared" ref="Q6:R8" si="1">M3</f>
         <v>21</v>
       </c>
-      <c r="R6" s="73">
-        <f>N3</f>
+      <c r="R6" s="63">
+        <f t="shared" si="1"/>
         <v>2.25</v>
       </c>
     </row>
@@ -2499,15 +2490,15 @@
         <v>2.35</v>
       </c>
       <c r="H7" s="2"/>
-      <c r="P7" s="35" t="s">
+      <c r="P7" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="Q7" s="32">
-        <f>M4</f>
+      <c r="Q7" s="30">
+        <f t="shared" si="1"/>
         <v>42</v>
       </c>
-      <c r="R7" s="50">
-        <f>N4</f>
+      <c r="R7" s="45">
+        <f t="shared" si="1"/>
         <v>4.5</v>
       </c>
     </row>
@@ -2534,22 +2525,22 @@
         <v>1.45</v>
       </c>
       <c r="H8" s="2"/>
-      <c r="K8" s="59"/>
-      <c r="L8" s="60" t="s">
+      <c r="K8" s="53"/>
+      <c r="L8" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="M8" s="61" t="s">
+      <c r="M8" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="P8" s="38" t="s">
+      <c r="P8" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="Q8" s="41">
-        <f>M5</f>
+      <c r="Q8" s="38">
+        <f t="shared" si="1"/>
         <v>56</v>
       </c>
-      <c r="R8" s="74">
-        <f>N5</f>
+      <c r="R8" s="64">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
     </row>
@@ -2576,23 +2567,23 @@
         <v>1.5</v>
       </c>
       <c r="H9" s="2"/>
-      <c r="K9" s="62" t="s">
+      <c r="K9" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="L9" s="63">
+      <c r="L9" s="57">
         <v>381</v>
       </c>
-      <c r="M9" s="64">
+      <c r="M9" s="58">
         <v>20</v>
       </c>
-      <c r="P9" s="38" t="s">
+      <c r="P9" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="Q9" s="39">
+      <c r="Q9" s="36">
         <f>SUM(Q6:Q8) * 1/3</f>
         <v>39.666666666666664</v>
       </c>
-      <c r="R9" s="74">
+      <c r="R9" s="64">
         <f>SQRT(R6^2 +R7^2 + R8^2 ) * 1/3</f>
         <v>2.6100766272276377</v>
       </c>
@@ -2620,23 +2611,23 @@
         <v>5.25</v>
       </c>
       <c r="H10" s="2"/>
-      <c r="K10" s="62" t="s">
+      <c r="K10" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L10" s="63">
+      <c r="L10" s="57">
         <v>6</v>
       </c>
-      <c r="M10" s="64">
+      <c r="M10" s="58">
         <v>3</v>
       </c>
-      <c r="P10" s="45" t="s">
+      <c r="P10" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="Q10" s="69">
+      <c r="Q10" s="42">
         <f>L10</f>
         <v>6</v>
       </c>
-      <c r="R10" s="70">
+      <c r="R10" s="43">
         <f>M10</f>
         <v>3</v>
       </c>
@@ -2664,23 +2655,23 @@
         <v>5.25</v>
       </c>
       <c r="H11" s="2"/>
-      <c r="K11" s="62" t="s">
+      <c r="K11" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="L11" s="63">
+      <c r="L11" s="57">
         <v>32</v>
       </c>
-      <c r="M11" s="64">
+      <c r="M11" s="58">
         <v>4</v>
       </c>
-      <c r="P11" s="45" t="s">
+      <c r="P11" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="Q11" s="76">
+      <c r="Q11" s="66">
         <f>L12-SUM(Q2:Q9)-Q10</f>
         <v>62.166666666666686</v>
       </c>
-      <c r="R11" s="77">
+      <c r="R11" s="67">
         <f>SQRT(M12^2 + R2^2 + R3^2 + R4^2 +R6^2 +R7^2 +R8^2 + R5^2 + R9^2 +R10^2 )</f>
         <v>24.682990094394967</v>
       </c>
@@ -2708,14 +2699,14 @@
         <v>4.8499999999999996</v>
       </c>
       <c r="H12" s="2"/>
-      <c r="K12" s="68" t="s">
+      <c r="K12" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="33">
+      <c r="L12">
         <f>L9+L11*2</f>
         <v>445</v>
       </c>
-      <c r="M12" s="34">
+      <c r="M12" s="31">
         <f>SQRT(M9^2+4*M11^2)</f>
         <v>21.540659228538015</v>
       </c>
@@ -2743,14 +2734,14 @@
         <v>3.4</v>
       </c>
       <c r="H13" s="2"/>
-      <c r="K13" s="65" t="s">
+      <c r="K13" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="37">
         <f>L12-L10-K6-M6</f>
         <v>156.375</v>
       </c>
-      <c r="M13" s="42">
+      <c r="M13" s="39">
         <f>SQRT(M12^2 + M10^2 + L6^2 + N6^2 )</f>
         <v>24.405429723731562</v>
       </c>
@@ -3805,13 +3796,13 @@
       <c r="B18" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="C18" s="81" t="s">
+      <c r="C18" s="71" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="82">
+      <c r="D18" s="72">
         <v>68.400000000000006</v>
       </c>
-      <c r="E18" s="82">
+      <c r="E18" s="72">
         <v>12.13232</v>
       </c>
       <c r="F18" s="12">
@@ -4254,23 +4245,23 @@
       <c r="G1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="78" t="s">
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="68" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="79" t="s">
+      <c r="Q1" s="69" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="80" t="s">
+      <c r="R1" s="70" t="s">
         <v>3</v>
       </c>
     </row>
@@ -4296,29 +4287,29 @@
       <c r="G2" s="10">
         <v>1.05</v>
       </c>
-      <c r="J2" s="43"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="87"/>
+      <c r="K2" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="N2" s="49" t="s">
+      <c r="N2" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="P2" s="71" t="s">
+      <c r="O2" s="91"/>
+      <c r="P2" s="61" t="s">
         <v>116</v>
       </c>
-      <c r="Q2" s="72">
-        <f>K3</f>
+      <c r="Q2" s="62">
+        <f t="shared" ref="Q2:R4" si="0">K3</f>
         <v>4.125</v>
       </c>
-      <c r="R2" s="73">
-        <f>L3</f>
+      <c r="R2" s="63">
+        <f t="shared" si="0"/>
         <v>1.875</v>
       </c>
     </row>
@@ -4347,34 +4338,34 @@
       <c r="I3" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="78">
         <v>39</v>
       </c>
-      <c r="K3" s="44">
+      <c r="K3" s="40">
         <f>J3/J5*K5</f>
         <v>4.125</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="33">
         <f>K3/K5*L5</f>
         <v>1.875</v>
       </c>
-      <c r="M3" s="44">
+      <c r="M3" s="40">
         <f>K3/K5*M5</f>
         <v>20.25</v>
       </c>
-      <c r="N3" s="50">
+      <c r="N3" s="45">
         <f>M3/M5*N5</f>
         <v>3.375</v>
       </c>
-      <c r="P3" s="35" t="s">
+      <c r="P3" s="32" t="s">
         <v>117</v>
       </c>
-      <c r="Q3" s="36">
-        <f>K4</f>
+      <c r="Q3" s="33">
+        <f t="shared" si="0"/>
         <v>8.25</v>
       </c>
-      <c r="R3" s="50">
-        <f>L4</f>
+      <c r="R3" s="45">
+        <f t="shared" si="0"/>
         <v>3.75</v>
       </c>
     </row>
@@ -4403,34 +4394,34 @@
       <c r="I4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="78">
         <v>78</v>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="40">
         <f>J4/J5*K5</f>
         <v>8.25</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="33">
         <f>K4/K5*L5</f>
         <v>3.75</v>
       </c>
-      <c r="M4" s="44">
+      <c r="M4" s="40">
         <f>K4/K5*M5</f>
         <v>40.5</v>
       </c>
-      <c r="N4" s="50">
+      <c r="N4" s="45">
         <f>M4/M5*N5</f>
         <v>6.75</v>
       </c>
-      <c r="P4" s="38" t="s">
+      <c r="P4" s="35" t="s">
         <v>118</v>
       </c>
-      <c r="Q4" s="39">
-        <f>K5</f>
+      <c r="Q4" s="36">
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="R4" s="74">
-        <f>L5</f>
+      <c r="R4" s="64">
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
@@ -4459,29 +4450,29 @@
       <c r="I5" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="89">
+      <c r="J5" s="79">
         <v>104</v>
       </c>
-      <c r="K5" s="83">
+      <c r="K5" s="73">
         <v>11</v>
       </c>
-      <c r="L5" s="84">
+      <c r="L5" s="74">
         <v>5</v>
       </c>
-      <c r="M5" s="83">
+      <c r="M5" s="73">
         <v>54</v>
       </c>
-      <c r="N5" s="85">
+      <c r="N5" s="75">
         <v>9</v>
       </c>
-      <c r="P5" s="71" t="s">
+      <c r="P5" s="61" t="s">
         <v>113</v>
       </c>
-      <c r="Q5" s="72">
+      <c r="Q5" s="62">
         <f>SUM(Q2:Q4) * 1/3</f>
         <v>7.791666666666667</v>
       </c>
-      <c r="R5" s="73">
+      <c r="R5" s="63">
         <f>SQRT(R2^2 + R3^2 + R4^2 ) * 1/3</f>
         <v>2.1750638560230313</v>
       </c>
@@ -4508,31 +4499,31 @@
       <c r="G6" s="10">
         <v>5.25</v>
       </c>
-      <c r="K6" s="52">
+      <c r="K6" s="46">
         <f>SUM(K3:K5)</f>
         <v>23.375</v>
       </c>
-      <c r="L6" s="52">
+      <c r="L6" s="46">
         <f>SQRT(L3^2 + L4^2 +L5^2)</f>
         <v>6.5251915680690935</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="47">
         <f>SUM(M3:M5)</f>
         <v>114.75</v>
       </c>
-      <c r="N6" s="52">
+      <c r="N6" s="46">
         <f>SQRT(N3^2 + N4^2 +N5^2)</f>
         <v>11.74534482252437</v>
       </c>
-      <c r="P6" s="71" t="s">
+      <c r="P6" s="61" t="s">
         <v>119</v>
       </c>
-      <c r="Q6" s="75">
-        <f>M3</f>
+      <c r="Q6" s="65">
+        <f t="shared" ref="Q6:R8" si="1">M3</f>
         <v>20.25</v>
       </c>
-      <c r="R6" s="73">
-        <f>N3</f>
+      <c r="R6" s="63">
+        <f t="shared" si="1"/>
         <v>3.375</v>
       </c>
     </row>
@@ -4558,15 +4549,15 @@
       <c r="G7" s="10">
         <v>18.3</v>
       </c>
-      <c r="P7" s="35" t="s">
+      <c r="P7" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="Q7" s="32">
-        <f>M4</f>
+      <c r="Q7" s="30">
+        <f t="shared" si="1"/>
         <v>40.5</v>
       </c>
-      <c r="R7" s="50">
-        <f>N4</f>
+      <c r="R7" s="45">
+        <f t="shared" si="1"/>
         <v>6.75</v>
       </c>
     </row>
@@ -4592,22 +4583,22 @@
       <c r="G8" s="10">
         <v>96.1</v>
       </c>
-      <c r="K8" s="59"/>
-      <c r="L8" s="60" t="s">
+      <c r="K8" s="53"/>
+      <c r="L8" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="M8" s="61" t="s">
+      <c r="M8" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="P8" s="38" t="s">
+      <c r="P8" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="Q8" s="41">
-        <f>M5</f>
+      <c r="Q8" s="38">
+        <f t="shared" si="1"/>
         <v>54</v>
       </c>
-      <c r="R8" s="74">
-        <f>N5</f>
+      <c r="R8" s="64">
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
     </row>
@@ -4633,23 +4624,23 @@
       <c r="G9" s="10">
         <v>111.05</v>
       </c>
-      <c r="K9" s="62" t="s">
+      <c r="K9" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="L9" s="86">
+      <c r="L9" s="76">
         <v>524</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="77">
         <v>47</v>
       </c>
-      <c r="P9" s="38" t="s">
+      <c r="P9" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="Q9" s="39">
+      <c r="Q9" s="36">
         <f>SUM(Q6:Q8) * 1/3</f>
         <v>38.25</v>
       </c>
-      <c r="R9" s="74">
+      <c r="R9" s="64">
         <f>SQRT(R6^2 +R7^2 + R8^2 ) * 1/3</f>
         <v>3.9151149408414567</v>
       </c>
@@ -4676,23 +4667,23 @@
       <c r="G10" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="K10" s="62" t="s">
+      <c r="K10" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L10" s="86">
+      <c r="L10" s="76">
         <v>31</v>
       </c>
-      <c r="M10" s="87">
+      <c r="M10" s="77">
         <v>6</v>
       </c>
-      <c r="P10" s="45" t="s">
+      <c r="P10" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="Q10" s="69">
+      <c r="Q10" s="42">
         <f>L10</f>
         <v>31</v>
       </c>
-      <c r="R10" s="70">
+      <c r="R10" s="43">
         <f>M10</f>
         <v>6</v>
       </c>
@@ -4719,23 +4710,23 @@
       <c r="G11" s="10">
         <v>111.85</v>
       </c>
-      <c r="K11" s="62" t="s">
+      <c r="K11" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="L11" s="86">
+      <c r="L11" s="76">
         <v>10</v>
       </c>
-      <c r="M11" s="87">
+      <c r="M11" s="77">
         <v>2</v>
       </c>
-      <c r="P11" s="45" t="s">
+      <c r="P11" s="41" t="s">
         <v>99</v>
       </c>
-      <c r="Q11" s="76">
+      <c r="Q11" s="66">
         <f>L12-SUM(Q2:Q9)-Q10</f>
         <v>328.83333333333331</v>
       </c>
-      <c r="R11" s="77">
+      <c r="R11" s="67">
         <f>SQRT(M12^2 + R2^2 + R3^2 + R4^2 +R6^2 +R7^2 +R8^2 + R5^2 + R9^2 +R10^2 )</f>
         <v>49.614416027781459</v>
       </c>
@@ -4762,14 +4753,14 @@
       <c r="G12" s="10">
         <v>0.8</v>
       </c>
-      <c r="K12" s="68" t="s">
+      <c r="K12" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="L12" s="33">
+      <c r="L12">
         <f>L9+L11*2</f>
         <v>544</v>
       </c>
-      <c r="M12" s="37">
+      <c r="M12" s="34">
         <f>SQRT(M9^2+4*M11^2)</f>
         <v>47.169905660283021</v>
       </c>
@@ -4796,14 +4787,14 @@
       <c r="G13" s="10">
         <v>1.1499999999999999</v>
       </c>
-      <c r="K13" s="65" t="s">
+      <c r="K13" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="L13" s="40">
+      <c r="L13" s="37">
         <f>L12-L10-K6-M6</f>
         <v>374.875</v>
       </c>
-      <c r="M13" s="66">
+      <c r="M13" s="60">
         <f>SQRT(M12^2 + M10^2 + L6^2 + N6^2 )</f>
         <v>49.411853335004544</v>
       </c>
@@ -5407,32 +5398,32 @@
       <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="86" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="46" t="s">
+      <c r="K1" s="88" t="s">
         <v>109</v>
       </c>
-      <c r="L1" s="47"/>
-      <c r="M1" s="47"/>
-      <c r="N1" s="48"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="94" t="s">
+      <c r="L1" s="89"/>
+      <c r="M1" s="89"/>
+      <c r="N1" s="90"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="Q1" s="94" t="s">
+      <c r="Q1" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="94" t="s">
+      <c r="R1" s="83" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="94" t="s">
+      <c r="T1" s="83" t="s">
         <v>111</v>
       </c>
-      <c r="U1" s="94" t="s">
+      <c r="U1" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="94" t="s">
+      <c r="V1" s="83" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5458,41 +5449,41 @@
       <c r="G2" s="2">
         <v>2.1</v>
       </c>
-      <c r="J2" s="43"/>
-      <c r="K2" s="38" t="s">
+      <c r="J2" s="87"/>
+      <c r="K2" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="L2" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="38" t="s">
+      <c r="M2" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="N2" s="49" t="s">
+      <c r="N2" s="44" t="s">
         <v>98</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="P2" s="91" t="s">
+      <c r="O2" s="91"/>
+      <c r="P2" s="81" t="s">
         <v>116</v>
       </c>
-      <c r="Q2" s="92">
-        <f>K3</f>
+      <c r="Q2" s="82">
+        <f t="shared" ref="Q2:R4" si="0">K3</f>
         <v>5.25</v>
       </c>
-      <c r="R2" s="92">
-        <f>L3</f>
+      <c r="R2" s="82">
+        <f t="shared" si="0"/>
         <v>2.625</v>
       </c>
-      <c r="T2" s="91" t="str">
+      <c r="T2" s="81" t="str">
         <f>P2</f>
         <v>NEFA-Palm</v>
       </c>
-      <c r="U2" s="95">
-        <f t="shared" ref="U2:V2" si="0">Q2</f>
+      <c r="U2" s="84">
+        <f t="shared" ref="U2:V2" si="1">Q2</f>
         <v>5.25</v>
       </c>
-      <c r="V2" s="95">
-        <f t="shared" si="0"/>
+      <c r="V2" s="84">
+        <f t="shared" si="1"/>
         <v>2.625</v>
       </c>
     </row>
@@ -5521,51 +5512,51 @@
       <c r="I3" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="J3" s="88">
+      <c r="J3" s="78">
         <v>39</v>
       </c>
-      <c r="K3" s="44">
+      <c r="K3" s="40">
         <f>J3/J5*K5</f>
         <v>5.25</v>
       </c>
-      <c r="L3" s="36">
+      <c r="L3" s="33">
         <f>K3/K5*L5</f>
         <v>2.625</v>
       </c>
-      <c r="M3" s="44">
+      <c r="M3" s="40">
         <f>K3/K5*M5</f>
         <v>21</v>
       </c>
-      <c r="N3" s="50">
+      <c r="N3" s="45">
         <f>M3/M5*N5</f>
         <v>3.375</v>
       </c>
-      <c r="P3" s="91" t="s">
+      <c r="P3" s="81" t="s">
         <v>117</v>
       </c>
-      <c r="Q3" s="92">
-        <f>K4</f>
+      <c r="Q3" s="82">
+        <f t="shared" si="0"/>
         <v>10.5</v>
       </c>
-      <c r="R3" s="92">
-        <f>L4</f>
+      <c r="R3" s="82">
+        <f t="shared" si="0"/>
         <v>5.25</v>
       </c>
-      <c r="T3" s="91" t="str">
-        <f t="shared" ref="T3:T4" si="1">P3</f>
+      <c r="T3" s="81" t="str">
+        <f t="shared" ref="T3:T4" si="2">P3</f>
         <v>NEFA-Ole</v>
       </c>
-      <c r="U3" s="95">
-        <f t="shared" ref="U3:U4" si="2">Q3</f>
+      <c r="U3" s="84">
+        <f t="shared" ref="U3:U4" si="3">Q3</f>
         <v>10.5</v>
       </c>
-      <c r="V3" s="95">
-        <f t="shared" ref="V3:V4" si="3">R3</f>
+      <c r="V3" s="84">
+        <f t="shared" ref="V3:V4" si="4">R3</f>
         <v>5.25</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A4" s="90">
+      <c r="A4" s="80">
         <v>3</v>
       </c>
       <c r="B4" s="7">
@@ -5589,51 +5580,51 @@
       <c r="I4" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="78">
         <v>78</v>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="40">
         <f>J4/J5*K5</f>
         <v>10.5</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="33">
         <f>K4/K5*L5</f>
         <v>5.25</v>
       </c>
-      <c r="M4" s="44">
+      <c r="M4" s="40">
         <f>K4/K5*M5</f>
         <v>42</v>
       </c>
-      <c r="N4" s="50">
+      <c r="N4" s="45">
         <f>M4/M5*N5</f>
         <v>6.75</v>
       </c>
-      <c r="P4" s="91" t="s">
+      <c r="P4" s="81" t="s">
         <v>118</v>
       </c>
-      <c r="Q4" s="92">
-        <f>K5</f>
+      <c r="Q4" s="82">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="R4" s="92">
-        <f>L5</f>
+      <c r="R4" s="82">
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="T4" s="91" t="str">
-        <f t="shared" si="1"/>
+      <c r="T4" s="81" t="str">
+        <f t="shared" si="2"/>
         <v>NEFA-Lino</v>
       </c>
-      <c r="U4" s="95">
-        <f t="shared" si="2"/>
+      <c r="U4" s="84">
+        <f t="shared" si="3"/>
         <v>14</v>
       </c>
-      <c r="V4" s="95">
-        <f t="shared" si="3"/>
+      <c r="V4" s="84">
+        <f t="shared" si="4"/>
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="90">
+      <c r="A5" s="80">
         <v>4</v>
       </c>
       <c r="B5" s="7">
@@ -5657,47 +5648,47 @@
       <c r="I5" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="89">
+      <c r="J5" s="79">
         <v>104</v>
       </c>
-      <c r="K5" s="83">
+      <c r="K5" s="73">
         <v>14</v>
       </c>
-      <c r="L5" s="84">
+      <c r="L5" s="74">
         <v>7</v>
       </c>
-      <c r="M5" s="83">
+      <c r="M5" s="73">
         <v>56</v>
       </c>
-      <c r="N5" s="85">
+      <c r="N5" s="75">
         <v>9</v>
       </c>
-      <c r="P5" s="91" t="s">
+      <c r="P5" s="81" t="s">
         <v>113</v>
       </c>
-      <c r="Q5" s="92">
+      <c r="Q5" s="82">
         <f>SUM(Q2:Q4) * 1/3</f>
         <v>9.9166666666666661</v>
       </c>
-      <c r="R5" s="92">
+      <c r="R5" s="82">
         <f>SQRT(R2^2 + R3^2 + R4^2 ) * 1/3</f>
         <v>3.045089398432244</v>
       </c>
-      <c r="T5" s="91" t="str">
+      <c r="T5" s="81" t="str">
         <f>P6</f>
         <v>TAG-Palm</v>
       </c>
-      <c r="U5" s="95">
-        <f t="shared" ref="U5:U7" si="4">Q6</f>
+      <c r="U5" s="84">
+        <f t="shared" ref="U5:U7" si="5">Q6</f>
         <v>21</v>
       </c>
-      <c r="V5" s="95">
-        <f t="shared" ref="V5:V7" si="5">R6</f>
+      <c r="V5" s="84">
+        <f t="shared" ref="V5:V7" si="6">R6</f>
         <v>3.375</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="90">
+      <c r="A6" s="80">
         <v>5</v>
       </c>
       <c r="B6" s="7">
@@ -5718,48 +5709,48 @@
       <c r="G6" s="2">
         <v>11.4</v>
       </c>
-      <c r="K6" s="52">
+      <c r="K6" s="46">
         <f>SUM(K3:K5)</f>
         <v>29.75</v>
       </c>
-      <c r="L6" s="52">
+      <c r="L6" s="46">
         <f>SQRT(L3^2 + L4^2 +L5^2)</f>
         <v>9.1352681952967316</v>
       </c>
-      <c r="M6" s="53">
+      <c r="M6" s="47">
         <f>SUM(M3:M5)</f>
         <v>119</v>
       </c>
-      <c r="N6" s="52">
+      <c r="N6" s="46">
         <f>SQRT(N3^2 + N4^2 +N5^2)</f>
         <v>11.74534482252437</v>
       </c>
-      <c r="P6" s="91" t="s">
+      <c r="P6" s="81" t="s">
         <v>119</v>
       </c>
-      <c r="Q6" s="91">
-        <f>M3</f>
+      <c r="Q6" s="81">
+        <f t="shared" ref="Q6:R8" si="7">M3</f>
         <v>21</v>
       </c>
-      <c r="R6" s="92">
-        <f>N3</f>
+      <c r="R6" s="82">
+        <f t="shared" si="7"/>
         <v>3.375</v>
       </c>
-      <c r="T6" s="91" t="str">
+      <c r="T6" s="81" t="str">
         <f>P7</f>
         <v>TAG-Ole</v>
       </c>
-      <c r="U6" s="95">
-        <f t="shared" si="4"/>
+      <c r="U6" s="84">
+        <f t="shared" si="5"/>
         <v>42</v>
       </c>
-      <c r="V6" s="95">
-        <f t="shared" si="5"/>
+      <c r="V6" s="84">
+        <f t="shared" si="6"/>
         <v>6.75</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="90">
+      <c r="A7" s="80">
         <v>6</v>
       </c>
       <c r="B7" s="7">
@@ -5780,32 +5771,32 @@
       <c r="G7" s="2">
         <v>66.05</v>
       </c>
-      <c r="P7" s="91" t="s">
+      <c r="P7" s="81" t="s">
         <v>120</v>
       </c>
-      <c r="Q7" s="91">
-        <f>M4</f>
+      <c r="Q7" s="81">
+        <f t="shared" si="7"/>
         <v>42</v>
       </c>
-      <c r="R7" s="92">
-        <f>N4</f>
+      <c r="R7" s="82">
+        <f t="shared" si="7"/>
         <v>6.75</v>
       </c>
-      <c r="T7" s="91" t="str">
+      <c r="T7" s="81" t="str">
         <f>P8</f>
         <v>TAG-Lino</v>
       </c>
-      <c r="U7" s="95">
-        <f t="shared" si="4"/>
+      <c r="U7" s="84">
+        <f t="shared" si="5"/>
         <v>56</v>
       </c>
-      <c r="V7" s="95">
-        <f t="shared" si="5"/>
+      <c r="V7" s="84">
+        <f t="shared" si="6"/>
         <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="90">
+      <c r="A8" s="80">
         <v>7</v>
       </c>
       <c r="B8" s="7">
@@ -5826,39 +5817,39 @@
       <c r="G8" s="2">
         <v>920.9</v>
       </c>
-      <c r="K8" s="59"/>
-      <c r="L8" s="60" t="s">
+      <c r="K8" s="53"/>
+      <c r="L8" s="54" t="s">
         <v>101</v>
       </c>
-      <c r="M8" s="61" t="s">
+      <c r="M8" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="P8" s="91" t="s">
+      <c r="P8" s="81" t="s">
         <v>121</v>
       </c>
-      <c r="Q8" s="91">
-        <f>M5</f>
+      <c r="Q8" s="81">
+        <f t="shared" si="7"/>
         <v>56</v>
       </c>
-      <c r="R8" s="92">
-        <f>N5</f>
+      <c r="R8" s="82">
+        <f t="shared" si="7"/>
         <v>9</v>
       </c>
-      <c r="T8" s="91" t="str">
-        <f>P10</f>
+      <c r="T8" s="81" t="str">
+        <f t="shared" ref="T8:V9" si="8">P10</f>
         <v>Amino Acids</v>
       </c>
-      <c r="U8" s="95">
-        <f>Q10</f>
+      <c r="U8" s="84">
+        <f t="shared" si="8"/>
         <v>163</v>
       </c>
-      <c r="V8" s="95">
-        <f>R10</f>
+      <c r="V8" s="84">
+        <f t="shared" si="8"/>
         <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="90">
+      <c r="A9" s="80">
         <v>8</v>
       </c>
       <c r="B9" s="7">
@@ -5879,41 +5870,41 @@
       <c r="G9" s="2">
         <v>986.8</v>
       </c>
-      <c r="K9" s="62" t="s">
+      <c r="K9" s="56" t="s">
         <v>100</v>
       </c>
-      <c r="L9" s="86">
+      <c r="L9" s="76">
         <v>331</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="77">
         <v>38</v>
       </c>
-      <c r="P9" s="91" t="s">
+      <c r="P9" s="81" t="s">
         <v>112</v>
       </c>
-      <c r="Q9" s="92">
+      <c r="Q9" s="82">
         <f>SUM(Q6:Q8) * 1/3</f>
         <v>39.666666666666664</v>
       </c>
-      <c r="R9" s="92">
+      <c r="R9" s="82">
         <f>SQRT(R6^2 +R7^2 + R8^2 ) * 1/3</f>
         <v>3.9151149408414567</v>
       </c>
-      <c r="T9" s="91" t="str">
-        <f>P11</f>
+      <c r="T9" s="81" t="str">
+        <f t="shared" si="8"/>
         <v>carbs</v>
       </c>
-      <c r="U9" s="95">
-        <f>Q11</f>
+      <c r="U9" s="84">
+        <f t="shared" si="8"/>
         <v>32</v>
       </c>
-      <c r="V9" s="95">
-        <f>R11</f>
+      <c r="V9" s="84">
+        <f t="shared" si="8"/>
         <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="90">
+      <c r="A10" s="80">
         <v>9</v>
       </c>
       <c r="B10" s="7">
@@ -5934,41 +5925,41 @@
       <c r="G10" s="2">
         <v>3.95</v>
       </c>
-      <c r="K10" s="62" t="s">
+      <c r="K10" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="L10" s="86">
+      <c r="L10" s="76">
         <v>12</v>
       </c>
-      <c r="M10" s="87">
+      <c r="M10" s="77">
         <v>2</v>
       </c>
-      <c r="P10" s="93" t="s">
+      <c r="P10" s="81" t="s">
         <v>124</v>
       </c>
-      <c r="Q10" s="91">
+      <c r="Q10" s="81">
         <f>L12</f>
         <v>163</v>
       </c>
-      <c r="R10" s="91">
+      <c r="R10" s="81">
         <f>M12</f>
         <v>50</v>
       </c>
-      <c r="T10" s="91" t="str">
+      <c r="T10" s="81" t="str">
         <f>P12</f>
         <v>others</v>
       </c>
-      <c r="U10" s="95">
+      <c r="U10" s="84">
         <f>L13- SUM(U2:U9)</f>
         <v>11.25</v>
       </c>
-      <c r="V10" s="95">
+      <c r="V10" s="84">
         <f>R12</f>
         <v>65.046190852689023</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="90">
+      <c r="A11" s="80">
         <v>10</v>
       </c>
       <c r="B11" s="7">
@@ -5989,29 +5980,29 @@
       <c r="G11" s="2">
         <v>920</v>
       </c>
-      <c r="K11" s="62" t="s">
+      <c r="K11" s="56" t="s">
         <v>103</v>
       </c>
-      <c r="L11" s="86">
+      <c r="L11" s="76">
         <v>32</v>
       </c>
-      <c r="M11" s="87">
+      <c r="M11" s="77">
         <v>5</v>
       </c>
-      <c r="P11" s="91" t="s">
+      <c r="P11" s="81" t="s">
         <v>115</v>
       </c>
-      <c r="Q11" s="91">
+      <c r="Q11" s="81">
         <f>L11</f>
         <v>32</v>
       </c>
-      <c r="R11" s="91">
+      <c r="R11" s="81">
         <f>M11</f>
         <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="90">
+      <c r="A12" s="80">
         <v>11</v>
       </c>
       <c r="B12" s="7">
@@ -6032,29 +6023,29 @@
       <c r="G12" s="2">
         <v>1.2</v>
       </c>
-      <c r="K12" s="67" t="s">
+      <c r="K12" t="s">
         <v>123</v>
       </c>
-      <c r="L12" s="86">
+      <c r="L12" s="76">
         <v>163</v>
       </c>
-      <c r="M12" s="86">
+      <c r="M12" s="76">
         <v>50</v>
       </c>
-      <c r="P12" s="91" t="s">
+      <c r="P12" s="81" t="s">
         <v>99</v>
       </c>
-      <c r="Q12" s="92">
+      <c r="Q12" s="82">
         <f>L13-SUM(Q2:Q9)-Q11-Q10</f>
         <v>-38.333333333333314</v>
       </c>
-      <c r="R12" s="92">
+      <c r="R12" s="82">
         <f>SQRT(M13^2 + R2^2 + R3^2 + R4^2 +R6^2 +R7^2 +R8^2 + R5^2 + R9^2 +R11^2  + R10^2)</f>
         <v>65.046190852689023</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="90">
+      <c r="A13" s="80">
         <v>12</v>
       </c>
       <c r="B13" s="7">
@@ -6075,26 +6066,26 @@
       <c r="G13" s="2">
         <v>2.15</v>
       </c>
-      <c r="K13" s="68" t="s">
+      <c r="K13" s="56" t="s">
         <v>114</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13">
         <f>L9+L10*2</f>
         <v>355</v>
       </c>
-      <c r="M13" s="37">
+      <c r="M13" s="34">
         <f>SQRT(M9^2+4*M10^2)</f>
         <v>38.209946349085598</v>
       </c>
-      <c r="P13" s="96" t="s">
+      <c r="P13" s="85" t="s">
         <v>125</v>
       </c>
-      <c r="T13" s="96" t="s">
+      <c r="T13" s="85" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="90">
+      <c r="A14" s="80">
         <v>13</v>
       </c>
       <c r="B14" s="7">
@@ -6115,20 +6106,20 @@
       <c r="G14" s="2">
         <v>1.65</v>
       </c>
-      <c r="K14" s="65" t="s">
+      <c r="K14" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="L14" s="40">
+      <c r="L14" s="37">
         <f>L13-L11-K6-M6-L12</f>
         <v>11.25</v>
       </c>
-      <c r="M14" s="66">
+      <c r="M14" s="60">
         <f>SQRT(M13^2 + M11^2 + L6^2 + N6^2 + M12^2 )</f>
         <v>64.856813443153371</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="90">
+      <c r="A15" s="80">
         <v>14</v>
       </c>
       <c r="B15" s="7">
@@ -6151,7 +6142,7 @@
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="90">
+      <c r="A16" s="80">
         <v>15</v>
       </c>
       <c r="B16" s="7">
@@ -6174,7 +6165,7 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="90">
+      <c r="A17" s="80">
         <v>16</v>
       </c>
       <c r="B17" s="7" t="s">
@@ -6197,7 +6188,7 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="90">
+      <c r="A18" s="80">
         <v>17</v>
       </c>
       <c r="B18" s="7">
@@ -6220,7 +6211,7 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="90">
+      <c r="A19" s="80">
         <v>18</v>
       </c>
       <c r="B19" s="7">
@@ -6243,7 +6234,7 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="90">
+      <c r="A20" s="80">
         <v>19</v>
       </c>
       <c r="B20" s="7" t="s">
@@ -6266,7 +6257,7 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="90">
+      <c r="A21" s="80">
         <v>20</v>
       </c>
       <c r="B21" s="7">
@@ -6289,7 +6280,7 @@
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="90">
+      <c r="A22" s="80">
         <v>21</v>
       </c>
       <c r="B22" s="7">
@@ -6312,7 +6303,7 @@
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="90">
+      <c r="A23" s="80">
         <v>22</v>
       </c>
       <c r="B23" s="7">
@@ -6335,7 +6326,7 @@
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="90">
+      <c r="A24" s="80">
         <v>23</v>
       </c>
       <c r="B24" s="7" t="s">
@@ -6358,7 +6349,7 @@
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="90">
+      <c r="A25" s="80">
         <v>24</v>
       </c>
       <c r="B25" s="7">
@@ -6381,7 +6372,7 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="90">
+      <c r="A26" s="80">
         <v>25</v>
       </c>
       <c r="B26" s="7">
@@ -6404,7 +6395,7 @@
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="90">
+      <c r="A27" s="80">
         <v>26</v>
       </c>
       <c r="B27" s="7">
@@ -6427,7 +6418,7 @@
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="90">
+      <c r="A28" s="80">
         <v>27</v>
       </c>
       <c r="B28" s="7">
@@ -6450,7 +6441,7 @@
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="90">
+      <c r="A29" s="80">
         <v>28</v>
       </c>
       <c r="B29" s="7">
@@ -6473,7 +6464,7 @@
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="90">
+      <c r="A30" s="80">
         <v>29</v>
       </c>
       <c r="B30" s="7">
@@ -6496,7 +6487,7 @@
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="90">
+      <c r="A31" s="80">
         <v>30</v>
       </c>
       <c r="B31" s="7">
@@ -6519,7 +6510,7 @@
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="90">
+      <c r="A32" s="80">
         <v>31</v>
       </c>
       <c r="B32" s="7">
@@ -6542,7 +6533,7 @@
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="90">
+      <c r="A33" s="80">
         <v>32</v>
       </c>
       <c r="B33" s="7">
@@ -6565,7 +6556,7 @@
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="90">
+      <c r="A34" s="80">
         <v>33</v>
       </c>
       <c r="B34" s="7">
@@ -6588,7 +6579,7 @@
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="90">
+      <c r="A35" s="80">
         <v>34</v>
       </c>
       <c r="B35" s="7">
@@ -6611,7 +6602,7 @@
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="90">
+      <c r="A36" s="80">
         <v>35</v>
       </c>
       <c r="B36" s="7" t="s">
@@ -6634,7 +6625,7 @@
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="90">
+      <c r="A37" s="80">
         <v>36</v>
       </c>
       <c r="B37" s="7">
@@ -6657,7 +6648,7 @@
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="90">
+      <c r="A38" s="80">
         <v>37</v>
       </c>
       <c r="B38" s="7">
@@ -6680,7 +6671,7 @@
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="90">
+      <c r="A39" s="80">
         <v>38</v>
       </c>
       <c r="B39" s="7">
@@ -6703,7 +6694,7 @@
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="90">
+      <c r="A40" s="80">
         <v>39</v>
       </c>
       <c r="B40" s="7">
@@ -6726,7 +6717,7 @@
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="90">
+      <c r="A41" s="80">
         <v>40</v>
       </c>
       <c r="B41" s="7">
@@ -6749,7 +6740,7 @@
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="90">
+      <c r="A42" s="80">
         <v>41</v>
       </c>
       <c r="B42" s="7">
@@ -6772,7 +6763,7 @@
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="90">
+      <c r="A43" s="80">
         <v>42</v>
       </c>
       <c r="B43" s="7">
@@ -6795,7 +6786,7 @@
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="90">
+      <c r="A44" s="80">
         <v>43</v>
       </c>
       <c r="B44" s="7">
@@ -6818,7 +6809,7 @@
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="90">
+      <c r="A45" s="80">
         <v>44</v>
       </c>
       <c r="B45" s="7" t="s">
@@ -6841,7 +6832,7 @@
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="90">
+      <c r="A46" s="80">
         <v>45</v>
       </c>
       <c r="B46" s="7">
@@ -6864,7 +6855,7 @@
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="90">
+      <c r="A47" s="80">
         <v>46</v>
       </c>
       <c r="B47" s="7">
@@ -6887,7 +6878,7 @@
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="90">
+      <c r="A48" s="80">
         <v>47</v>
       </c>
       <c r="B48" s="7">
@@ -6910,7 +6901,7 @@
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="90">
+      <c r="A49" s="80">
         <v>48</v>
       </c>
       <c r="B49" s="7" t="s">
@@ -6933,7 +6924,7 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="90">
+      <c r="A50" s="80">
         <v>49</v>
       </c>
       <c r="B50" s="7">
@@ -6956,7 +6947,7 @@
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="90">
+      <c r="A51" s="80">
         <v>50</v>
       </c>
       <c r="B51" s="7">
@@ -6979,7 +6970,7 @@
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="90">
+      <c r="A52" s="80">
         <v>51</v>
       </c>
       <c r="B52" s="7">
@@ -7002,7 +6993,7 @@
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="90">
+      <c r="A53" s="80">
         <v>52</v>
       </c>
       <c r="B53" s="7">
@@ -7025,7 +7016,7 @@
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="90">
+      <c r="A54" s="80">
         <v>53</v>
       </c>
       <c r="B54" s="7">
@@ -7048,7 +7039,7 @@
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="90">
+      <c r="A55" s="80">
         <v>54</v>
       </c>
       <c r="B55" s="7" t="s">
@@ -7071,7 +7062,7 @@
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="90">
+      <c r="A56" s="80">
         <v>55</v>
       </c>
       <c r="B56" s="7">
@@ -7094,7 +7085,7 @@
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="90">
+      <c r="A57" s="80">
         <v>56</v>
       </c>
       <c r="B57" s="7">
@@ -7117,7 +7108,7 @@
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="90">
+      <c r="A58" s="80">
         <v>57</v>
       </c>
       <c r="B58" s="7">
@@ -7140,7 +7131,7 @@
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="90">
+      <c r="A59" s="80">
         <v>58</v>
       </c>
       <c r="B59" s="7">
@@ -7163,7 +7154,7 @@
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="90">
+      <c r="A60" s="80">
         <v>59</v>
       </c>
       <c r="B60" s="7">

--- a/CI compiled.xlsx
+++ b/CI compiled.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/boyuan/Desktop/Harvard/Research/Energy Metabolism Atlas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58678F0-042B-844D-AD95-0B0F6BF9D571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFB1ECBB-D10D-1242-85ED-7D1378185BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="22360" windowWidth="30240" windowHeight="17280" activeTab="1" xr2:uid="{C27F82BD-D1C2-DF4B-9AB6-A06FDDA3A96C}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" activeTab="4" xr2:uid="{C27F82BD-D1C2-DF4B-9AB6-A06FDDA3A96C}"/>
   </bookViews>
   <sheets>
     <sheet name="Fasted base " sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="475" uniqueCount="126">
   <si>
     <t>flux.index</t>
   </si>
@@ -227,9 +227,6 @@
   </si>
   <si>
     <t>67-69</t>
-  </si>
-  <si>
-    <t>5-6</t>
   </si>
   <si>
     <t>3-4</t>
@@ -688,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -873,7 +870,6 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -907,6 +903,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="16" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2179,18 +2179,18 @@
         <v>47</v>
       </c>
       <c r="H1" s="1"/>
-      <c r="J1" s="86" t="s">
+      <c r="J1" s="85" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" s="87" t="s">
+        <v>108</v>
+      </c>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="68" t="s">
         <v>110</v>
-      </c>
-      <c r="K1" s="88" t="s">
-        <v>109</v>
-      </c>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="68" t="s">
-        <v>111</v>
       </c>
       <c r="Q1" s="69" t="s">
         <v>2</v>
@@ -2222,22 +2222,22 @@
         <v>7.55</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="J2" s="87"/>
+      <c r="J2" s="86"/>
       <c r="K2" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="N2" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="N2" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="O2" s="91"/>
+      <c r="O2" s="90"/>
       <c r="P2" s="61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q2" s="62">
         <f t="shared" ref="Q2:R4" si="0">K3</f>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J3" s="48">
         <v>39</v>
@@ -2294,7 +2294,7 @@
         <v>2.25</v>
       </c>
       <c r="P3" s="32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q3" s="33">
         <f t="shared" si="0"/>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J4" s="48">
         <v>78</v>
@@ -2351,7 +2351,7 @@
         <v>4.5</v>
       </c>
       <c r="P4" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q4" s="36">
         <f t="shared" si="0"/>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J5" s="49">
         <v>104</v>
@@ -2405,7 +2405,7 @@
         <v>6</v>
       </c>
       <c r="P5" s="61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q5" s="62">
         <f>SUM(Q2:Q4) * 1/3</f>
@@ -2456,7 +2456,7 @@
         <v>7.8302298816829126</v>
       </c>
       <c r="P6" s="61" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q6" s="65">
         <f t="shared" ref="Q6:R8" si="1">M3</f>
@@ -2491,7 +2491,7 @@
       </c>
       <c r="H7" s="2"/>
       <c r="P7" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q7" s="30">
         <f t="shared" si="1"/>
@@ -2527,13 +2527,13 @@
       <c r="H8" s="2"/>
       <c r="K8" s="53"/>
       <c r="L8" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="M8" s="55" t="s">
-        <v>102</v>
-      </c>
       <c r="P8" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q8" s="38">
         <f t="shared" si="1"/>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="H9" s="2"/>
       <c r="K9" s="56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L9" s="57">
         <v>381</v>
@@ -2577,7 +2577,7 @@
         <v>20</v>
       </c>
       <c r="P9" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q9" s="36">
         <f>SUM(Q6:Q8) * 1/3</f>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="H10" s="2"/>
       <c r="K10" s="56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L10" s="57">
         <v>6</v>
@@ -2621,7 +2621,7 @@
         <v>3</v>
       </c>
       <c r="P10" s="41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q10" s="42">
         <f>L10</f>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="H11" s="2"/>
       <c r="K11" s="56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L11" s="57">
         <v>32</v>
@@ -2665,7 +2665,7 @@
         <v>4</v>
       </c>
       <c r="P11" s="41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q11" s="66">
         <f>L12-SUM(Q2:Q9)-Q10</f>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H12" s="2"/>
       <c r="K12" s="56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L12">
         <f>L9+L11*2</f>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="H13" s="2"/>
       <c r="K13" s="59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L13" s="37">
         <f>L12-L10-K6-M6</f>
@@ -3679,7 +3679,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C13" s="24" t="s">
         <v>53</v>
@@ -3794,7 +3794,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C18" s="71" t="s">
         <v>59</v>
@@ -4213,50 +4213,50 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A445C644-8496-5A44-B0FE-2B566BCCFFC0}">
-  <dimension ref="A1:R38"/>
+  <dimension ref="A1:R37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="32.1640625" customWidth="1"/>
-    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="93" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="93" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="17" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8"/>
-      <c r="B1" s="14" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="92" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="86" t="s">
+      <c r="J1" s="85" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" s="87" t="s">
+        <v>108</v>
+      </c>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="68" t="s">
         <v>110</v>
-      </c>
-      <c r="K1" s="88" t="s">
-        <v>109</v>
-      </c>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="68" t="s">
-        <v>111</v>
       </c>
       <c r="Q1" s="69" t="s">
         <v>2</v>
@@ -4266,47 +4266,47 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="15">
+      <c r="B2" s="28">
         <v>10</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="25">
-        <v>10.9</v>
-      </c>
-      <c r="E2" s="25">
-        <v>5.4911209999999997</v>
-      </c>
-      <c r="F2" s="10">
-        <v>2.1</v>
-      </c>
-      <c r="G2" s="10">
-        <v>1.05</v>
-      </c>
-      <c r="J2" s="87"/>
+      <c r="D2" s="29">
+        <v>31.8</v>
+      </c>
+      <c r="E2" s="29">
+        <v>5.2469478000000001</v>
+      </c>
+      <c r="F2" s="2">
+        <v>5.5</v>
+      </c>
+      <c r="G2" s="2">
+        <v>0.9</v>
+      </c>
+      <c r="J2" s="86"/>
       <c r="K2" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="N2" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="N2" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="O2" s="91"/>
+      <c r="O2" s="90"/>
       <c r="P2" s="61" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q2" s="62">
         <f t="shared" ref="Q2:R4" si="0">K3</f>
-        <v>4.125</v>
+        <v>12</v>
       </c>
       <c r="R2" s="63">
         <f t="shared" si="0"/>
@@ -4314,36 +4314,36 @@
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="2">
         <v>11</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="25">
-        <v>53.6</v>
-      </c>
-      <c r="E3" s="25">
-        <v>9.3041319999999992</v>
-      </c>
-      <c r="F3" s="10">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="G3" s="10">
-        <v>1.8</v>
+      <c r="D3" s="29">
+        <v>59</v>
+      </c>
+      <c r="E3" s="29">
+        <v>9.0893648999999996</v>
+      </c>
+      <c r="F3" s="2">
+        <v>10.3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1.55</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J3" s="78">
         <v>39</v>
       </c>
       <c r="K3" s="40">
         <f>J3/J5*K5</f>
-        <v>4.125</v>
+        <v>12</v>
       </c>
       <c r="L3" s="33">
         <f>K3/K5*L5</f>
@@ -4351,18 +4351,18 @@
       </c>
       <c r="M3" s="40">
         <f>K3/K5*M5</f>
-        <v>20.25</v>
+        <v>22.125</v>
       </c>
       <c r="N3" s="45">
         <f>M3/M5*N5</f>
         <v>3.375</v>
       </c>
       <c r="P3" s="32" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q3" s="33">
         <f t="shared" si="0"/>
-        <v>8.25</v>
+        <v>24</v>
       </c>
       <c r="R3" s="45">
         <f t="shared" si="0"/>
@@ -4370,36 +4370,36 @@
       </c>
     </row>
     <row r="4" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="2">
         <v>12</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="25">
-        <v>524.4</v>
-      </c>
-      <c r="E4" s="25">
-        <v>47.296599999999998</v>
-      </c>
-      <c r="F4" s="10">
+      <c r="D4" s="29">
+        <v>575.6</v>
+      </c>
+      <c r="E4" s="29">
+        <v>28.039443200000001</v>
+      </c>
+      <c r="F4" s="2">
         <v>100</v>
       </c>
-      <c r="G4" s="10">
-        <v>9</v>
+      <c r="G4" s="2">
+        <v>4.8499999999999996</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J4" s="78">
         <v>78</v>
       </c>
       <c r="K4" s="40">
         <f>J4/J5*K5</f>
-        <v>8.25</v>
+        <v>24</v>
       </c>
       <c r="L4" s="33">
         <f>K4/K5*L5</f>
@@ -4407,18 +4407,18 @@
       </c>
       <c r="M4" s="40">
         <f>K4/K5*M5</f>
-        <v>40.5</v>
+        <v>44.25</v>
       </c>
       <c r="N4" s="45">
         <f>M4/M5*N5</f>
         <v>6.75</v>
       </c>
       <c r="P4" s="35" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="Q4" s="36">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="R4" s="64">
         <f t="shared" si="0"/>
@@ -4426,51 +4426,51 @@
       </c>
     </row>
     <row r="5" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="2">
         <v>13</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="20">
-        <v>524.4</v>
-      </c>
-      <c r="E5" s="20">
-        <v>47.296599999999998</v>
-      </c>
-      <c r="F5" s="10">
+      <c r="D5" s="26">
+        <v>575.6</v>
+      </c>
+      <c r="E5" s="26">
+        <v>28.039443200000001</v>
+      </c>
+      <c r="F5" s="2">
         <v>100</v>
       </c>
-      <c r="G5" s="10">
-        <v>9</v>
+      <c r="G5" s="2">
+        <v>4.8499999999999996</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J5" s="79">
         <v>104</v>
       </c>
       <c r="K5" s="73">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="L5" s="74">
         <v>5</v>
       </c>
       <c r="M5" s="73">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="N5" s="75">
         <v>9</v>
       </c>
       <c r="P5" s="61" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q5" s="62">
         <f>SUM(Q2:Q4) * 1/3</f>
-        <v>7.791666666666667</v>
+        <v>22.666666666666668</v>
       </c>
       <c r="R5" s="63">
         <f>SQRT(R2^2 + R3^2 + R4^2 ) * 1/3</f>
@@ -4478,30 +4478,30 @@
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="28">
+        <v>19</v>
+      </c>
+      <c r="C6" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="25">
-        <v>525.5</v>
-      </c>
-      <c r="E6" s="25">
-        <v>27.628579999999999</v>
-      </c>
-      <c r="F6" s="10">
-        <v>100.2</v>
-      </c>
-      <c r="G6" s="10">
-        <v>5.25</v>
+      <c r="D6" s="29">
+        <v>121.9</v>
+      </c>
+      <c r="E6" s="29">
+        <v>60.93</v>
+      </c>
+      <c r="F6" s="2">
+        <v>21.2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10.55</v>
       </c>
       <c r="K6" s="46">
         <f>SUM(K3:K5)</f>
-        <v>23.375</v>
+        <v>68</v>
       </c>
       <c r="L6" s="46">
         <f>SQRT(L3^2 + L4^2 +L5^2)</f>
@@ -4509,18 +4509,18 @@
       </c>
       <c r="M6" s="47">
         <f>SUM(M3:M5)</f>
-        <v>114.75</v>
+        <v>125.375</v>
       </c>
       <c r="N6" s="46">
         <f>SQRT(N3^2 + N4^2 +N5^2)</f>
         <v>11.74534482252437</v>
       </c>
       <c r="P6" s="61" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q6" s="65">
         <f t="shared" ref="Q6:R8" si="1">M3</f>
-        <v>20.25</v>
+        <v>22.125</v>
       </c>
       <c r="R6" s="63">
         <f t="shared" si="1"/>
@@ -4528,33 +4528,33 @@
       </c>
     </row>
     <row r="7" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="15">
-        <v>19</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>14</v>
-      </c>
-      <c r="D7" s="25">
-        <v>192.3</v>
-      </c>
-      <c r="E7" s="25">
-        <v>96.031289999999998</v>
-      </c>
-      <c r="F7" s="10">
-        <v>36.700000000000003</v>
-      </c>
-      <c r="G7" s="10">
-        <v>18.3</v>
+      <c r="B7" s="28">
+        <v>20</v>
+      </c>
+      <c r="C7" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="29">
+        <v>1158.5</v>
+      </c>
+      <c r="E7" s="29">
+        <v>148.80208709999999</v>
+      </c>
+      <c r="F7" s="2">
+        <v>201.3</v>
+      </c>
+      <c r="G7" s="2">
+        <v>25.85</v>
       </c>
       <c r="P7" s="32" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="Q7" s="30">
         <f t="shared" si="1"/>
-        <v>40.5</v>
+        <v>44.25</v>
       </c>
       <c r="R7" s="45">
         <f t="shared" si="1"/>
@@ -4562,40 +4562,40 @@
       </c>
     </row>
     <row r="8" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="15">
-        <v>20</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="25">
-        <v>1904.4</v>
-      </c>
-      <c r="E8" s="25">
-        <v>503.93889999999999</v>
-      </c>
-      <c r="F8" s="10">
-        <v>363.1</v>
-      </c>
-      <c r="G8" s="10">
-        <v>96.1</v>
+      <c r="B8" s="28">
+        <v>21</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="29">
+        <v>1096.8</v>
+      </c>
+      <c r="E8" s="29">
+        <v>187.1593882</v>
+      </c>
+      <c r="F8" s="2">
+        <v>190.6</v>
+      </c>
+      <c r="G8" s="2">
+        <v>32.5</v>
       </c>
       <c r="K8" s="53"/>
       <c r="L8" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="M8" s="55" t="s">
-        <v>102</v>
-      </c>
       <c r="P8" s="35" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q8" s="38">
         <f t="shared" si="1"/>
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="R8" s="64">
         <f t="shared" si="1"/>
@@ -4603,42 +4603,42 @@
       </c>
     </row>
     <row r="9" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="15">
-        <v>21</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="25">
-        <v>1762</v>
-      </c>
-      <c r="E9" s="25">
-        <v>582.39369999999997</v>
-      </c>
-      <c r="F9" s="10">
-        <v>336</v>
-      </c>
-      <c r="G9" s="10">
-        <v>111.05</v>
+      <c r="B9" s="2">
+        <v>22</v>
+      </c>
+      <c r="C9" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="29">
+        <v>266.60000000000002</v>
+      </c>
+      <c r="E9" s="29">
+        <v>11.286872000000001</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46.3</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1.95</v>
       </c>
       <c r="K9" s="56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L9" s="76">
-        <v>524</v>
+        <v>576</v>
       </c>
       <c r="M9" s="77">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="P9" s="35" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q9" s="36">
         <f>SUM(Q6:Q8) * 1/3</f>
-        <v>38.25</v>
+        <v>41.791666666666664</v>
       </c>
       <c r="R9" s="64">
         <f>SQRT(R6^2 +R7^2 + R8^2 ) * 1/3</f>
@@ -4646,42 +4646,42 @@
       </c>
     </row>
     <row r="10" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="15">
-        <v>22</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="25">
-        <v>265.7</v>
-      </c>
-      <c r="E10" s="25">
-        <v>12.163489999999999</v>
-      </c>
-      <c r="F10" s="10">
-        <v>50.7</v>
-      </c>
-      <c r="G10" s="10">
-        <v>2.2999999999999998</v>
+      <c r="B10" s="2">
+        <v>23</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="29">
+        <v>823.1</v>
+      </c>
+      <c r="E10" s="29">
+        <v>185.24419330000001</v>
+      </c>
+      <c r="F10" s="2">
+        <v>143</v>
+      </c>
+      <c r="G10" s="2">
+        <v>32.200000000000003</v>
       </c>
       <c r="K10" s="56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L10" s="76">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="M10" s="77">
         <v>6</v>
       </c>
       <c r="P10" s="41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q10" s="42">
         <f>L10</f>
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="R10" s="43">
         <f>M10</f>
@@ -4689,670 +4689,648 @@
       </c>
     </row>
     <row r="11" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="15">
-        <v>23</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="25">
-        <v>1503.1</v>
-      </c>
-      <c r="E11" s="25">
-        <v>586.49839999999995</v>
-      </c>
-      <c r="F11" s="10">
-        <v>286.60000000000002</v>
-      </c>
-      <c r="G11" s="10">
-        <v>111.85</v>
+      <c r="B11" s="2">
+        <v>25</v>
+      </c>
+      <c r="C11" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="29">
+        <v>46.1</v>
+      </c>
+      <c r="E11" s="29">
+        <v>5.8256595000000004</v>
+      </c>
+      <c r="F11" s="2">
+        <v>8</v>
+      </c>
+      <c r="G11" s="2">
+        <v>1</v>
       </c>
       <c r="K11" s="56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L11" s="76">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M11" s="77">
         <v>2</v>
       </c>
       <c r="P11" s="41" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q11" s="66">
         <f>L12-SUM(Q2:Q9)-Q10</f>
-        <v>328.83333333333331</v>
+        <v>298.16666666666663</v>
       </c>
       <c r="R11" s="67">
         <f>SQRT(M12^2 + R2^2 + R3^2 + R4^2 +R6^2 +R7^2 +R8^2 + R5^2 + R9^2 +R10^2 )</f>
-        <v>49.614416027781459</v>
+        <v>32.196122092229956</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A12" s="8">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="15">
-        <v>25</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" s="25">
-        <v>23.1</v>
-      </c>
-      <c r="E12" s="25">
-        <v>4.1323939999999997</v>
-      </c>
-      <c r="F12" s="10">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="G12" s="10">
-        <v>0.8</v>
+      <c r="B12" s="28">
+        <v>27</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="29">
+        <v>156.6</v>
+      </c>
+      <c r="E12" s="29">
+        <v>6.6036923999999999</v>
+      </c>
+      <c r="F12" s="2">
+        <v>27.2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>1.1499999999999999</v>
       </c>
       <c r="K12" s="56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L12">
         <f>L9+L11*2</f>
-        <v>544</v>
+        <v>594</v>
       </c>
       <c r="M12" s="34">
         <f>SQRT(M9^2+4*M11^2)</f>
-        <v>47.169905660283021</v>
+        <v>28.284271247461902</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="15">
-        <v>27</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>20</v>
-      </c>
-      <c r="D13" s="25">
-        <v>143.5</v>
-      </c>
-      <c r="E13" s="25">
-        <v>6.0861429999999999</v>
-      </c>
-      <c r="F13" s="10">
-        <v>27.4</v>
-      </c>
-      <c r="G13" s="10">
-        <v>1.1499999999999999</v>
+      <c r="B13" s="2">
+        <v>28</v>
+      </c>
+      <c r="C13" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="29">
+        <v>248</v>
+      </c>
+      <c r="E13" s="29">
+        <v>5.7883411999999996</v>
+      </c>
+      <c r="F13" s="2">
+        <v>43.1</v>
+      </c>
+      <c r="G13" s="2">
+        <v>1</v>
       </c>
       <c r="K13" s="59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L13" s="37">
         <f>L12-L10-K6-M6</f>
-        <v>374.875</v>
+        <v>362.625</v>
       </c>
       <c r="M13" s="60">
         <f>SQRT(M12^2 + M10^2 + L6^2 + N6^2 )</f>
-        <v>49.411853335004544</v>
+        <v>31.88308720936541</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A14" s="8">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="15">
+      <c r="B14" s="2">
+        <v>29</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="29">
+        <v>404.7</v>
+      </c>
+      <c r="E14" s="29">
+        <v>6.7134292999999996</v>
+      </c>
+      <c r="F14" s="2">
+        <v>70.3</v>
+      </c>
+      <c r="G14" s="2">
+        <v>1.1499999999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>5</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="D15" s="26">
+        <v>449.3</v>
+      </c>
+      <c r="E15" s="26">
+        <v>39.466121100000002</v>
+      </c>
+      <c r="F15" s="2">
+        <v>78.099999999999994</v>
+      </c>
+      <c r="G15" s="2">
+        <v>6.85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="91">
+        <v>46148</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" s="29">
+        <v>216.8</v>
+      </c>
+      <c r="E16" s="29">
+        <v>17.435652699999999</v>
+      </c>
+      <c r="F16" s="2">
+        <v>37.700000000000003</v>
+      </c>
+      <c r="G16" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2">
+        <v>53</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="26">
+        <v>32</v>
+      </c>
+      <c r="E17" s="26">
+        <v>8.6614246000000001</v>
+      </c>
+      <c r="F17" s="2">
+        <v>5.6</v>
+      </c>
+      <c r="G17" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2">
+        <v>55</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="26">
+        <v>103.3</v>
+      </c>
+      <c r="E18" s="26">
+        <v>5.9409158</v>
+      </c>
+      <c r="F18" s="2">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="G18" s="2">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="29">
+        <v>74.7</v>
+      </c>
+      <c r="E19" s="29">
+        <v>8.1228321999999995</v>
+      </c>
+      <c r="F19" s="2">
+        <v>13</v>
+      </c>
+      <c r="G19" s="2">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2">
+        <v>59</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" s="26">
+        <v>55.2</v>
+      </c>
+      <c r="E20" s="26">
+        <v>7.2374235000000002</v>
+      </c>
+      <c r="F20" s="2">
+        <v>9.6</v>
+      </c>
+      <c r="G20" s="2">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>6</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D21" s="26">
+        <v>229.6</v>
+      </c>
+      <c r="E21" s="26">
+        <v>40.863793200000003</v>
+      </c>
+      <c r="F21" s="2">
+        <v>39.9</v>
+      </c>
+      <c r="G21" s="2">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>61</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="D14" s="25">
-        <v>259</v>
-      </c>
-      <c r="E14" s="25">
-        <v>4.8382860000000001</v>
-      </c>
-      <c r="F14" s="10">
-        <v>49.4</v>
-      </c>
-      <c r="G14" s="10">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A15" s="8">
-        <v>14</v>
-      </c>
-      <c r="B15" s="15">
+      <c r="D22" s="26">
+        <v>72.7</v>
+      </c>
+      <c r="E22" s="26">
+        <v>5.9966790000000003</v>
+      </c>
+      <c r="F22" s="2">
+        <v>12.6</v>
+      </c>
+      <c r="G22" s="2">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="29">
+        <v>13.1</v>
+      </c>
+      <c r="E23" s="29">
+        <v>6.5330985000000004</v>
+      </c>
+      <c r="F23" s="2">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G23" s="2">
+        <v>1.1000000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="2">
+        <v>63</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>64</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E25" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>25</v>
+      </c>
+      <c r="B26" s="2">
+        <v>65</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E26" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>66</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E27" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>67</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" s="26">
+        <v>14.4</v>
+      </c>
+      <c r="E28" s="26">
+        <v>0.48404940000000002</v>
+      </c>
+      <c r="F28" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G28" s="2">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>28</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C29" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D29" s="29">
+        <v>8.9</v>
+      </c>
+      <c r="E29" s="29">
+        <v>1.5799072999999999</v>
+      </c>
+      <c r="F29" s="2">
+        <v>1.6</v>
+      </c>
+      <c r="G29" s="2">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="C15" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="D15" s="25">
-        <v>403.3</v>
-      </c>
-      <c r="E15" s="25">
-        <v>7.1402489999999998</v>
-      </c>
-      <c r="F15" s="10">
-        <v>76.900000000000006</v>
-      </c>
-      <c r="G15" s="10">
-        <v>1.35</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A16" s="8">
-        <v>15</v>
-      </c>
-      <c r="B16" s="15">
+      <c r="B30" s="2">
+        <v>69</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="26">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E30" s="26">
+        <v>1.6122745999999999</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>7</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D16" s="20">
-        <v>414.5</v>
-      </c>
-      <c r="E16" s="20">
-        <v>51.236780000000003</v>
-      </c>
-      <c r="F16" s="10">
-        <v>79</v>
-      </c>
-      <c r="G16" s="10">
-        <v>9.8000000000000007</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="8">
-        <v>16</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="25">
-        <v>184.6</v>
-      </c>
-      <c r="E17" s="25">
-        <v>18.904820000000001</v>
-      </c>
-      <c r="F17" s="10">
-        <v>35.200000000000003</v>
-      </c>
-      <c r="G17" s="10">
-        <v>3.6</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="8">
-        <v>17</v>
-      </c>
-      <c r="B18" s="15">
-        <v>53</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="20">
-        <v>40.299999999999997</v>
-      </c>
-      <c r="E18" s="20">
-        <v>13.239470000000001</v>
-      </c>
-      <c r="F18" s="10">
-        <v>7.7</v>
-      </c>
-      <c r="G18" s="10">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="8">
-        <v>18</v>
-      </c>
-      <c r="B19" s="15">
-        <v>55</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D19" s="20">
-        <v>98.4</v>
-      </c>
-      <c r="E19" s="20">
-        <v>10.233790000000001</v>
-      </c>
-      <c r="F19" s="10">
-        <v>18.8</v>
-      </c>
-      <c r="G19" s="10">
-        <v>1.95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="8">
-        <v>19</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="25">
-        <v>69.8</v>
-      </c>
-      <c r="E20" s="25">
-        <v>10.789680000000001</v>
-      </c>
-      <c r="F20" s="10">
-        <v>13.3</v>
-      </c>
-      <c r="G20" s="10">
-        <v>2.0499999999999998</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="8">
-        <v>20</v>
-      </c>
-      <c r="B21" s="15">
-        <v>59</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="20">
-        <v>41.5</v>
-      </c>
-      <c r="E21" s="20">
-        <v>13.183339999999999</v>
-      </c>
-      <c r="F21" s="10">
-        <v>7.9</v>
-      </c>
-      <c r="G21" s="10">
-        <v>2.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="8">
-        <v>21</v>
-      </c>
-      <c r="B22" s="15">
+      <c r="D31" s="26">
+        <v>1119.2</v>
+      </c>
+      <c r="E31" s="26">
+        <v>185.05699039999999</v>
+      </c>
+      <c r="F31" s="2">
+        <v>194.4</v>
+      </c>
+      <c r="G31" s="2">
+        <v>32.15</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>71</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D32" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E32" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>72</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D33" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E33" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>73</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D34" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E34" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>8</v>
+      </c>
+      <c r="C35" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="D22" s="20">
-        <v>220.2</v>
-      </c>
-      <c r="E22" s="20">
-        <v>53.713419999999999</v>
-      </c>
-      <c r="F22" s="10">
-        <v>42</v>
-      </c>
-      <c r="G22" s="10">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="8">
-        <v>22</v>
-      </c>
-      <c r="B23" s="15">
-        <v>61</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="20">
-        <v>66.599999999999994</v>
-      </c>
-      <c r="E23" s="20">
-        <v>5.8595480000000002</v>
-      </c>
-      <c r="F23" s="10">
-        <v>12.7</v>
-      </c>
-      <c r="G23" s="10">
-        <v>1.1000000000000001</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="8">
-        <v>23</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="25">
-        <v>25.8</v>
-      </c>
-      <c r="E24" s="25">
-        <v>12.37598</v>
-      </c>
-      <c r="F24" s="10">
-        <v>4.9000000000000004</v>
-      </c>
-      <c r="G24" s="10">
-        <v>2.35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="8">
-        <v>24</v>
-      </c>
-      <c r="B25" s="15">
-        <v>63</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="20">
-        <v>159180.1</v>
-      </c>
-      <c r="E25" s="20">
-        <v>79512.36</v>
-      </c>
-      <c r="F25" s="10">
-        <v>30353.3</v>
-      </c>
-      <c r="G25" s="10">
-        <v>15161.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="8">
-        <v>25</v>
-      </c>
-      <c r="B26" s="15">
-        <v>64</v>
-      </c>
-      <c r="C26" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D26" s="20">
-        <v>159180.1</v>
-      </c>
-      <c r="E26" s="20">
-        <v>79512.36</v>
-      </c>
-      <c r="F26" s="10">
-        <v>30353.3</v>
-      </c>
-      <c r="G26" s="10">
-        <v>15161.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="8">
-        <v>26</v>
-      </c>
-      <c r="B27" s="15">
-        <v>65</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D27" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E27" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G27" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="8">
-        <v>27</v>
-      </c>
-      <c r="B28" s="15">
-        <v>66</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="D35" s="29">
+        <v>37.799999999999997</v>
+      </c>
+      <c r="E35" s="29">
+        <v>6.2767844999999998</v>
+      </c>
+      <c r="F35" s="2">
+        <v>6.6</v>
+      </c>
+      <c r="G35" s="2">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
         <v>35</v>
       </c>
-      <c r="D28" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G28" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="8">
-        <v>28</v>
-      </c>
-      <c r="B29" s="15">
-        <v>67</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D29" s="20">
-        <v>14.3</v>
-      </c>
-      <c r="E29" s="20">
-        <v>0.51727420000000002</v>
-      </c>
-      <c r="F29" s="10">
-        <v>2.7</v>
-      </c>
-      <c r="G29" s="10">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="8">
-        <v>29</v>
-      </c>
-      <c r="B30" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="C30" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D30" s="25">
-        <v>10.1</v>
-      </c>
-      <c r="E30" s="25">
-        <v>1.8357140000000001</v>
-      </c>
-      <c r="F30" s="10">
-        <v>1.9</v>
-      </c>
-      <c r="G30" s="10">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="8">
-        <v>30</v>
-      </c>
-      <c r="B31" s="15">
-        <v>69</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D31" s="20">
-        <v>3.8</v>
-      </c>
-      <c r="E31" s="20">
-        <v>1.8859870000000001</v>
-      </c>
-      <c r="F31" s="10">
-        <v>0.7</v>
-      </c>
-      <c r="G31" s="10">
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="8">
-        <v>31</v>
-      </c>
-      <c r="B32" s="15">
+      <c r="B36" s="2">
+        <v>9</v>
+      </c>
+      <c r="C36" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D32" s="20">
-        <v>1754.6</v>
-      </c>
-      <c r="E32" s="20">
-        <v>582.21900000000005</v>
-      </c>
-      <c r="F32" s="10">
-        <v>334.6</v>
-      </c>
-      <c r="G32" s="10">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="8">
-        <v>32</v>
-      </c>
-      <c r="B33" s="15">
-        <v>71</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F33" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G33" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="8">
-        <v>33</v>
-      </c>
-      <c r="B34" s="15">
-        <v>72</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D34" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F34" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G34" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="8">
-        <v>34</v>
-      </c>
-      <c r="B35" s="15">
-        <v>73</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D35" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E35" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F35" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="G35" s="11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="8">
-        <v>35</v>
-      </c>
-      <c r="B36" s="15">
-        <v>8</v>
-      </c>
-      <c r="C36" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D36" s="25">
-        <v>30.6</v>
-      </c>
-      <c r="E36" s="25">
-        <v>5.8554680000000001</v>
-      </c>
-      <c r="F36" s="10">
-        <v>5.8</v>
-      </c>
-      <c r="G36" s="10">
-        <v>1.1499999999999999</v>
+      <c r="D36" s="29">
+        <v>471.3</v>
+      </c>
+      <c r="E36" s="29">
+        <v>23.6300466</v>
+      </c>
+      <c r="F36" s="2">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="G36" s="2">
+        <v>4.0999999999999996</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="8">
-        <v>36</v>
-      </c>
-      <c r="B37" s="15">
-        <v>9</v>
-      </c>
-      <c r="C37" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D37" s="25">
-        <v>422.3</v>
-      </c>
-      <c r="E37" s="25">
-        <v>25.020689999999998</v>
-      </c>
-      <c r="F37" s="10">
-        <v>80.5</v>
-      </c>
-      <c r="G37" s="10">
-        <v>4.8</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="4"/>
+      <c r="A37" s="4"/>
+      <c r="B37"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5371,25 +5349,36 @@
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="27" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.83203125" style="13" customWidth="1"/>
-    <col min="4" max="4" width="11.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14" style="13" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45" style="13" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.83203125" style="19" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.6640625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="29" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="4.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
@@ -5398,32 +5387,32 @@
       <c r="G1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="J1" s="86" t="s">
+      <c r="J1" s="85" t="s">
+        <v>109</v>
+      </c>
+      <c r="K1" s="87" t="s">
+        <v>108</v>
+      </c>
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="89"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="K1" s="88" t="s">
-        <v>109</v>
-      </c>
-      <c r="L1" s="89"/>
-      <c r="M1" s="89"/>
-      <c r="N1" s="90"/>
-      <c r="O1" s="91"/>
-      <c r="P1" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q1" s="83" t="s">
+      <c r="Q1" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="R1" s="83" t="s">
+      <c r="R1" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="T1" s="83" t="s">
-        <v>111</v>
-      </c>
-      <c r="U1" s="83" t="s">
+      <c r="T1" s="82" t="s">
+        <v>110</v>
+      </c>
+      <c r="U1" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="V1" s="83" t="s">
+      <c r="V1" s="82" t="s">
         <v>3</v>
       </c>
     </row>
@@ -5431,938 +5420,938 @@
       <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="28">
         <v>10</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="25">
-        <v>14.1</v>
-      </c>
-      <c r="E2" s="25">
-        <v>7.0356459999999998</v>
+      <c r="D2" s="29">
+        <v>24.4</v>
+      </c>
+      <c r="E2" s="29">
+        <v>7.7641220000000004</v>
       </c>
       <c r="F2" s="2">
-        <v>4.3</v>
+        <v>6.8</v>
       </c>
       <c r="G2" s="2">
-        <v>2.1</v>
-      </c>
-      <c r="J2" s="87"/>
+        <v>2.15</v>
+      </c>
+      <c r="J2" s="86"/>
       <c r="K2" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="L2" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="M2" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="L2" s="38" t="s">
+      <c r="N2" s="44" t="s">
         <v>97</v>
       </c>
-      <c r="M2" s="35" t="s">
-        <v>96</v>
-      </c>
-      <c r="N2" s="44" t="s">
-        <v>98</v>
-      </c>
-      <c r="O2" s="91"/>
-      <c r="P2" s="81" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q2" s="82">
+      <c r="O2" s="90"/>
+      <c r="P2" s="80" t="s">
+        <v>115</v>
+      </c>
+      <c r="Q2" s="81">
         <f t="shared" ref="Q2:R4" si="0">K3</f>
-        <v>5.25</v>
-      </c>
-      <c r="R2" s="82">
+        <v>9</v>
+      </c>
+      <c r="R2" s="81">
         <f t="shared" si="0"/>
-        <v>2.625</v>
-      </c>
-      <c r="T2" s="81" t="str">
+        <v>3</v>
+      </c>
+      <c r="T2" s="80" t="str">
         <f>P2</f>
         <v>NEFA-Palm</v>
       </c>
-      <c r="U2" s="84">
+      <c r="U2" s="83">
         <f t="shared" ref="U2:V2" si="1">Q2</f>
-        <v>5.25</v>
-      </c>
-      <c r="V2" s="84">
+        <v>9</v>
+      </c>
+      <c r="V2" s="83">
         <f t="shared" si="1"/>
-        <v>2.625</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="28">
         <v>11</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D3" s="25">
-        <v>56.4</v>
-      </c>
-      <c r="E3" s="25">
-        <v>8.7241769999999992</v>
+      <c r="D3" s="29">
+        <v>57.6</v>
+      </c>
+      <c r="E3" s="29">
+        <v>8.2677460000000007</v>
       </c>
       <c r="F3" s="2">
-        <v>17</v>
+        <v>16.100000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>2.65</v>
+        <v>2.2999999999999998</v>
       </c>
       <c r="I3" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="J3" s="78">
         <v>39</v>
       </c>
       <c r="K3" s="40">
         <f>J3/J5*K5</f>
-        <v>5.25</v>
+        <v>9</v>
       </c>
       <c r="L3" s="33">
         <f>K3/K5*L5</f>
-        <v>2.625</v>
+        <v>3</v>
       </c>
       <c r="M3" s="40">
         <f>K3/K5*M5</f>
-        <v>21</v>
+        <v>21.75</v>
       </c>
       <c r="N3" s="45">
         <f>M3/M5*N5</f>
-        <v>3.375</v>
-      </c>
-      <c r="P3" s="81" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q3" s="82">
+        <v>3</v>
+      </c>
+      <c r="P3" s="80" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q3" s="81">
         <f t="shared" si="0"/>
-        <v>10.5</v>
-      </c>
-      <c r="R3" s="82">
+        <v>18</v>
+      </c>
+      <c r="R3" s="81">
         <f t="shared" si="0"/>
-        <v>5.25</v>
-      </c>
-      <c r="T3" s="81" t="str">
+        <v>6</v>
+      </c>
+      <c r="T3" s="80" t="str">
         <f t="shared" ref="T3:T4" si="2">P3</f>
         <v>NEFA-Ole</v>
       </c>
-      <c r="U3" s="84">
+      <c r="U3" s="83">
         <f t="shared" ref="U3:U4" si="3">Q3</f>
-        <v>10.5</v>
-      </c>
-      <c r="V3" s="84">
+        <v>18</v>
+      </c>
+      <c r="V3" s="83">
         <f t="shared" ref="V3:V4" si="4">R3</f>
-        <v>5.25</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A4" s="80">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="28">
         <v>12</v>
       </c>
-      <c r="C4" s="24" t="s">
+      <c r="C4" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="25">
-        <v>330.8</v>
-      </c>
-      <c r="E4" s="25">
-        <v>37.764268999999999</v>
+      <c r="D4" s="29">
+        <v>358.4</v>
+      </c>
+      <c r="E4" s="29">
+        <v>43.651867000000003</v>
       </c>
       <c r="F4" s="2">
         <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="I4" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="J4" s="78">
         <v>78</v>
       </c>
       <c r="K4" s="40">
         <f>J4/J5*K5</f>
-        <v>10.5</v>
+        <v>18</v>
       </c>
       <c r="L4" s="33">
         <f>K4/K5*L5</f>
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="M4" s="40">
         <f>K4/K5*M5</f>
-        <v>42</v>
+        <v>43.5</v>
       </c>
       <c r="N4" s="45">
         <f>M4/M5*N5</f>
-        <v>6.75</v>
-      </c>
-      <c r="P4" s="81" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q4" s="82">
+        <v>6</v>
+      </c>
+      <c r="P4" s="80" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q4" s="81">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="R4" s="82">
+        <v>24</v>
+      </c>
+      <c r="R4" s="81">
         <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="T4" s="81" t="str">
+        <v>8</v>
+      </c>
+      <c r="T4" s="80" t="str">
         <f t="shared" si="2"/>
         <v>NEFA-Lino</v>
       </c>
-      <c r="U4" s="84">
+      <c r="U4" s="83">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="V4" s="84">
+        <v>24</v>
+      </c>
+      <c r="V4" s="83">
         <f t="shared" si="4"/>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="80">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="2">
         <v>13</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="20">
-        <v>330.8</v>
-      </c>
-      <c r="E5" s="20">
-        <v>37.764268999999999</v>
+      <c r="D5" s="26">
+        <v>358.4</v>
+      </c>
+      <c r="E5" s="26">
+        <v>43.651867000000003</v>
       </c>
       <c r="F5" s="2">
         <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
       <c r="I5" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J5" s="79">
         <v>104</v>
       </c>
       <c r="K5" s="73">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="L5" s="74">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M5" s="73">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N5" s="75">
-        <v>9</v>
-      </c>
-      <c r="P5" s="81" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q5" s="82">
+        <v>8</v>
+      </c>
+      <c r="P5" s="80" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q5" s="81">
         <f>SUM(Q2:Q4) * 1/3</f>
-        <v>9.9166666666666661</v>
-      </c>
-      <c r="R5" s="82">
+        <v>17</v>
+      </c>
+      <c r="R5" s="81">
         <f>SQRT(R2^2 + R3^2 + R4^2 ) * 1/3</f>
-        <v>3.045089398432244</v>
-      </c>
-      <c r="T5" s="81" t="str">
+        <v>3.4801021696368504</v>
+      </c>
+      <c r="T5" s="80" t="str">
         <f>P6</f>
         <v>TAG-Palm</v>
       </c>
-      <c r="U5" s="84">
+      <c r="U5" s="83">
         <f t="shared" ref="U5:U7" si="5">Q6</f>
-        <v>21</v>
-      </c>
-      <c r="V5" s="84">
+        <v>21.75</v>
+      </c>
+      <c r="V5" s="83">
         <f t="shared" ref="V5:V7" si="6">R6</f>
-        <v>3.375</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A6" s="80">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="2">
         <v>14</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C6" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="25">
-        <v>352.8</v>
-      </c>
-      <c r="E6" s="25">
-        <v>37.760859000000004</v>
+      <c r="D6" s="29">
+        <v>372.6</v>
+      </c>
+      <c r="E6" s="29">
+        <v>42.107722000000003</v>
       </c>
       <c r="F6" s="2">
-        <v>106.7</v>
+        <v>104</v>
       </c>
       <c r="G6" s="2">
-        <v>11.4</v>
+        <v>11.75</v>
       </c>
       <c r="K6" s="46">
         <f>SUM(K3:K5)</f>
-        <v>29.75</v>
+        <v>51</v>
       </c>
       <c r="L6" s="46">
         <f>SQRT(L3^2 + L4^2 +L5^2)</f>
-        <v>9.1352681952967316</v>
+        <v>10.440306508910551</v>
       </c>
       <c r="M6" s="47">
         <f>SUM(M3:M5)</f>
-        <v>119</v>
+        <v>123.25</v>
       </c>
       <c r="N6" s="46">
         <f>SQRT(N3^2 + N4^2 +N5^2)</f>
-        <v>11.74534482252437</v>
-      </c>
-      <c r="P6" s="81" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q6" s="81">
+        <v>10.440306508910551</v>
+      </c>
+      <c r="P6" s="80" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q6" s="80">
         <f t="shared" ref="Q6:R8" si="7">M3</f>
-        <v>21</v>
-      </c>
-      <c r="R6" s="82">
+        <v>21.75</v>
+      </c>
+      <c r="R6" s="81">
         <f t="shared" si="7"/>
-        <v>3.375</v>
-      </c>
-      <c r="T6" s="81" t="str">
+        <v>3</v>
+      </c>
+      <c r="T6" s="80" t="str">
         <f>P7</f>
         <v>TAG-Ole</v>
       </c>
-      <c r="U6" s="84">
+      <c r="U6" s="83">
         <f t="shared" si="5"/>
-        <v>42</v>
-      </c>
-      <c r="V6" s="84">
+        <v>43.5</v>
+      </c>
+      <c r="V6" s="83">
         <f t="shared" si="6"/>
-        <v>6.75</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="80">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="7">
+      <c r="B7" s="2">
         <v>19</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="25">
-        <v>437.2</v>
-      </c>
-      <c r="E7" s="25">
-        <v>218.58193700000001</v>
+      <c r="D7" s="29">
+        <v>79.3</v>
+      </c>
+      <c r="E7" s="29">
+        <v>39.597920999999999</v>
       </c>
       <c r="F7" s="2">
-        <v>132.19999999999999</v>
+        <v>22.1</v>
       </c>
       <c r="G7" s="2">
-        <v>66.05</v>
-      </c>
-      <c r="P7" s="81" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q7" s="81">
+        <v>11.05</v>
+      </c>
+      <c r="P7" s="80" t="s">
+        <v>119</v>
+      </c>
+      <c r="Q7" s="80">
         <f t="shared" si="7"/>
-        <v>42</v>
-      </c>
-      <c r="R7" s="82">
+        <v>43.5</v>
+      </c>
+      <c r="R7" s="81">
         <f t="shared" si="7"/>
-        <v>6.75</v>
-      </c>
-      <c r="T7" s="81" t="str">
+        <v>6</v>
+      </c>
+      <c r="T7" s="80" t="str">
         <f>P8</f>
         <v>TAG-Lino</v>
       </c>
-      <c r="U7" s="84">
+      <c r="U7" s="83">
         <f t="shared" si="5"/>
-        <v>56</v>
-      </c>
-      <c r="V7" s="84">
+        <v>58</v>
+      </c>
+      <c r="V7" s="83">
         <f t="shared" si="6"/>
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A8" s="80">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="2">
         <v>20</v>
       </c>
-      <c r="C8" s="24" t="s">
+      <c r="C8" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="25">
-        <v>7281.7</v>
-      </c>
-      <c r="E8" s="25">
-        <v>3046.1327160000001</v>
+      <c r="D8" s="29">
+        <v>2307.9</v>
+      </c>
+      <c r="E8" s="29">
+        <v>574.28884800000003</v>
       </c>
       <c r="F8" s="2">
-        <v>2201.4</v>
+        <v>644</v>
       </c>
       <c r="G8" s="2">
-        <v>920.9</v>
+        <v>160.30000000000001</v>
       </c>
       <c r="K8" s="53"/>
       <c r="L8" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="55" t="s">
         <v>101</v>
       </c>
-      <c r="M8" s="55" t="s">
-        <v>102</v>
-      </c>
-      <c r="P8" s="81" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q8" s="81">
+      <c r="P8" s="80" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q8" s="80">
         <f t="shared" si="7"/>
-        <v>56</v>
-      </c>
-      <c r="R8" s="82">
+        <v>58</v>
+      </c>
+      <c r="R8" s="81">
         <f t="shared" si="7"/>
-        <v>9</v>
-      </c>
-      <c r="T8" s="81" t="str">
+        <v>8</v>
+      </c>
+      <c r="T8" s="80" t="str">
         <f t="shared" ref="T8:V9" si="8">P10</f>
         <v>Amino Acids</v>
       </c>
-      <c r="U8" s="84">
+      <c r="U8" s="83">
         <f t="shared" si="8"/>
-        <v>163</v>
-      </c>
-      <c r="V8" s="84">
+        <v>148</v>
+      </c>
+      <c r="V8" s="83">
         <f t="shared" si="8"/>
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A9" s="80">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="2">
         <v>21</v>
       </c>
-      <c r="C9" s="24" t="s">
+      <c r="C9" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="25">
-        <v>6528.2</v>
-      </c>
-      <c r="E9" s="25">
-        <v>3264.1338900000001</v>
+      <c r="D9" s="29">
+        <v>2208.5</v>
+      </c>
+      <c r="E9" s="29">
+        <v>693.26638500000001</v>
       </c>
       <c r="F9" s="2">
-        <v>1973.6</v>
+        <v>616.29999999999995</v>
       </c>
       <c r="G9" s="2">
-        <v>986.8</v>
+        <v>193.45</v>
       </c>
       <c r="K9" s="56" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L9" s="76">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="M9" s="77">
-        <v>38</v>
-      </c>
-      <c r="P9" s="81" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q9" s="82">
+        <v>44</v>
+      </c>
+      <c r="P9" s="80" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q9" s="81">
         <f>SUM(Q6:Q8) * 1/3</f>
-        <v>39.666666666666664</v>
-      </c>
-      <c r="R9" s="82">
+        <v>41.083333333333336</v>
+      </c>
+      <c r="R9" s="81">
         <f>SQRT(R6^2 +R7^2 + R8^2 ) * 1/3</f>
-        <v>3.9151149408414567</v>
-      </c>
-      <c r="T9" s="81" t="str">
+        <v>3.4801021696368504</v>
+      </c>
+      <c r="T9" s="80" t="str">
         <f t="shared" si="8"/>
         <v>carbs</v>
       </c>
-      <c r="U9" s="84">
+      <c r="U9" s="83">
         <f t="shared" si="8"/>
-        <v>32</v>
-      </c>
-      <c r="V9" s="84">
+        <v>35</v>
+      </c>
+      <c r="V9" s="83">
         <f t="shared" si="8"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A10" s="80">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="2">
         <v>22</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="25">
-        <v>282.3</v>
-      </c>
-      <c r="E10" s="25">
-        <v>12.915710000000001</v>
+      <c r="D10" s="29">
+        <v>288.7</v>
+      </c>
+      <c r="E10" s="29">
+        <v>13.250714</v>
       </c>
       <c r="F10" s="2">
-        <v>85.3</v>
+        <v>80.599999999999994</v>
       </c>
       <c r="G10" s="2">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K10" s="56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="L10" s="76">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="M10" s="77">
         <v>2</v>
       </c>
-      <c r="P10" s="81" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q10" s="81">
+      <c r="P10" s="80" t="s">
+        <v>123</v>
+      </c>
+      <c r="Q10" s="80">
         <f>L12</f>
-        <v>163</v>
-      </c>
-      <c r="R10" s="81">
+        <v>148</v>
+      </c>
+      <c r="R10" s="80">
         <f>M12</f>
-        <v>50</v>
-      </c>
-      <c r="T10" s="81" t="str">
+        <v>41</v>
+      </c>
+      <c r="T10" s="80" t="str">
         <f>P12</f>
         <v>others</v>
       </c>
-      <c r="U10" s="84">
+      <c r="U10" s="83">
         <f>L13- SUM(U2:U9)</f>
-        <v>11.25</v>
-      </c>
-      <c r="V10" s="84">
+        <v>22.75</v>
+      </c>
+      <c r="V10" s="83">
         <f>R12</f>
-        <v>65.046190852689023</v>
+        <v>62.539765127654761</v>
       </c>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A11" s="80">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="2">
         <v>23</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D11" s="25">
-        <v>6581.4</v>
-      </c>
-      <c r="E11" s="25">
-        <v>3043.2581060000002</v>
+      <c r="D11" s="29">
+        <v>1930.7</v>
+      </c>
+      <c r="E11" s="29">
+        <v>699.86754099999996</v>
       </c>
       <c r="F11" s="2">
-        <v>1989.7</v>
+        <v>538.79999999999995</v>
       </c>
       <c r="G11" s="2">
-        <v>920</v>
+        <v>195.3</v>
       </c>
       <c r="K11" s="56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L11" s="76">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="M11" s="77">
-        <v>5</v>
-      </c>
-      <c r="P11" s="81" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q11" s="81">
+        <v>6</v>
+      </c>
+      <c r="P11" s="80" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q11" s="80">
         <f>L11</f>
-        <v>32</v>
-      </c>
-      <c r="R11" s="81">
+        <v>35</v>
+      </c>
+      <c r="R11" s="80">
         <f>M11</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A12" s="80">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="7">
+      <c r="B12" s="2">
         <v>25</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="28" t="s">
         <v>19</v>
       </c>
-      <c r="D12" s="25">
-        <v>22</v>
-      </c>
-      <c r="E12" s="25">
-        <v>4.044842</v>
+      <c r="D12" s="29">
+        <v>45.9</v>
+      </c>
+      <c r="E12" s="29">
+        <v>5.4828840000000003</v>
       </c>
       <c r="F12" s="2">
-        <v>6.7</v>
+        <v>12.8</v>
       </c>
       <c r="G12" s="2">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="K12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L12" s="76">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="M12" s="76">
-        <v>50</v>
-      </c>
-      <c r="P12" s="81" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q12" s="82">
+        <v>41</v>
+      </c>
+      <c r="P12" s="80" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q12" s="81">
         <f>L13-SUM(Q2:Q9)-Q11-Q10</f>
-        <v>-38.333333333333314</v>
-      </c>
-      <c r="R12" s="82">
+        <v>-35.333333333333343</v>
+      </c>
+      <c r="R12" s="81">
         <f>SQRT(M13^2 + R2^2 + R3^2 + R4^2 +R6^2 +R7^2 +R8^2 + R5^2 + R9^2 +R11^2  + R10^2)</f>
-        <v>65.046190852689023</v>
+        <v>62.539765127654761</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A13" s="80">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="7">
+      <c r="B13" s="2">
         <v>27</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="25">
-        <v>152.6</v>
-      </c>
-      <c r="E13" s="25">
-        <v>7.0015390000000002</v>
+      <c r="D13" s="29">
+        <v>166.8</v>
+      </c>
+      <c r="E13" s="29">
+        <v>6.8507210000000001</v>
       </c>
       <c r="F13" s="2">
-        <v>46.1</v>
+        <v>46.5</v>
       </c>
       <c r="G13" s="2">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="K13" s="56" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L13">
         <f>L9+L10*2</f>
-        <v>355</v>
+        <v>380</v>
       </c>
       <c r="M13" s="34">
         <f>SQRT(M9^2+4*M10^2)</f>
-        <v>38.209946349085598</v>
-      </c>
-      <c r="P13" s="85" t="s">
+        <v>44.181444068749045</v>
+      </c>
+      <c r="P13" s="84" t="s">
+        <v>124</v>
+      </c>
+      <c r="T13" s="84" t="s">
         <v>125</v>
       </c>
-      <c r="T13" s="85" t="s">
-        <v>126</v>
-      </c>
     </row>
     <row r="14" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="80">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="7">
+      <c r="B14" s="2">
         <v>28</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="D14" s="25">
-        <v>250.9</v>
-      </c>
-      <c r="E14" s="25">
-        <v>5.4303379999999999</v>
+      <c r="D14" s="29">
+        <v>238.6</v>
+      </c>
+      <c r="E14" s="29">
+        <v>5.8626459999999998</v>
       </c>
       <c r="F14" s="2">
-        <v>75.8</v>
+        <v>66.599999999999994</v>
       </c>
       <c r="G14" s="2">
         <v>1.65</v>
       </c>
       <c r="K14" s="59" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="L14" s="37">
         <f>L13-L11-K6-M6-L12</f>
-        <v>11.25</v>
+        <v>22.75</v>
       </c>
       <c r="M14" s="60">
         <f>SQRT(M13^2 + M11^2 + L6^2 + N6^2 + M12^2 )</f>
-        <v>64.856813443153371</v>
+        <v>62.345809803065357</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A15" s="80">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="7">
+      <c r="B15" s="2">
         <v>29</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="D15" s="25">
-        <v>405.4</v>
-      </c>
-      <c r="E15" s="25">
-        <v>6.7217890000000002</v>
+      <c r="D15" s="29">
+        <v>405.7</v>
+      </c>
+      <c r="E15" s="29">
+        <v>6.7713239999999999</v>
       </c>
       <c r="F15" s="2">
-        <v>122.5</v>
+        <v>113.2</v>
       </c>
       <c r="G15" s="2">
-        <v>2.0499999999999998</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="A16" s="80">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="7">
+      <c r="B16" s="2">
         <v>5</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D16" s="20">
-        <v>345.2</v>
-      </c>
-      <c r="E16" s="20">
-        <v>42.164645999999998</v>
+      <c r="D16" s="26">
+        <v>343.1</v>
+      </c>
+      <c r="E16" s="26">
+        <v>37.828442000000003</v>
       </c>
       <c r="F16" s="2">
-        <v>104.3</v>
+        <v>95.7</v>
       </c>
       <c r="G16" s="2">
-        <v>12.8</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="80">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="24" t="s">
+      <c r="B17" s="91">
+        <v>46148</v>
+      </c>
+      <c r="C17" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="25">
-        <v>97.1</v>
-      </c>
-      <c r="E17" s="25">
-        <v>25.195466</v>
+      <c r="D17" s="29">
+        <v>96.6</v>
+      </c>
+      <c r="E17" s="29">
+        <v>25.403022</v>
       </c>
       <c r="F17" s="2">
-        <v>29.3</v>
+        <v>26.9</v>
       </c>
       <c r="G17" s="2">
-        <v>7.65</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A18" s="80">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="7">
+      <c r="B18" s="2">
         <v>51</v>
       </c>
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D18" s="26">
+        <v>31.3</v>
+      </c>
+      <c r="E18" s="26">
+        <v>15.605</v>
+      </c>
+      <c r="F18" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G18" s="2">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2">
+        <v>52</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="20">
-        <v>37.5</v>
-      </c>
-      <c r="E18" s="20">
-        <v>18.754999999999999</v>
-      </c>
-      <c r="F18" s="2">
-        <v>11.3</v>
-      </c>
-      <c r="G18" s="2">
-        <v>5.7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" s="80">
-        <v>18</v>
-      </c>
-      <c r="B19" s="7">
-        <v>52</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="D19" s="26">
+        <v>30.5</v>
+      </c>
+      <c r="E19" s="26">
+        <v>15.223750000000001</v>
+      </c>
+      <c r="F19" s="2">
+        <v>8.5</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D19" s="20">
-        <v>34.4</v>
-      </c>
-      <c r="E19" s="20">
-        <v>17.18</v>
-      </c>
-      <c r="F19" s="2">
-        <v>10.4</v>
-      </c>
-      <c r="G19" s="2">
-        <v>5.2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" s="80">
-        <v>19</v>
-      </c>
-      <c r="B20" s="7" t="s">
+      <c r="C20" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="D20" s="29">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="E20" s="29">
+        <v>17.571249999999999</v>
+      </c>
+      <c r="F20" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="G20" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="2">
+        <v>53</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="25">
-        <v>58.6</v>
-      </c>
-      <c r="E20" s="25">
-        <v>29.30875</v>
-      </c>
-      <c r="F20" s="2">
-        <v>17.7</v>
-      </c>
-      <c r="G20" s="2">
-        <v>8.85</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" s="80">
-        <v>20</v>
-      </c>
-      <c r="B21" s="7">
-        <v>53</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="D21" s="26">
+        <v>33.6</v>
+      </c>
+      <c r="E21" s="26">
+        <v>16.798749999999998</v>
+      </c>
+      <c r="F21" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="G21" s="2">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="2">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D21" s="20">
-        <v>56.3</v>
-      </c>
-      <c r="E21" s="20">
-        <v>28.105</v>
-      </c>
-      <c r="F21" s="2">
-        <v>17</v>
-      </c>
-      <c r="G21" s="2">
-        <v>8.5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" s="80">
-        <v>21</v>
-      </c>
-      <c r="B22" s="7">
-        <v>54</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="D22" s="26">
+        <v>32.4</v>
+      </c>
+      <c r="E22" s="26">
+        <v>16.226875</v>
+      </c>
+      <c r="F22" s="2">
+        <v>9</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>55</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D22" s="20">
-        <v>42.6</v>
-      </c>
-      <c r="E22" s="20">
-        <v>21.283124999999998</v>
-      </c>
-      <c r="F22" s="2">
-        <v>12.9</v>
-      </c>
-      <c r="G22" s="2">
-        <v>6.4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" s="80">
-        <v>22</v>
-      </c>
-      <c r="B23" s="7">
-        <v>55</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" s="20">
-        <v>57.8</v>
-      </c>
-      <c r="E23" s="20">
-        <v>28.9175</v>
+      <c r="D23" s="26">
+        <v>62.5</v>
+      </c>
+      <c r="E23" s="26">
+        <v>31.254999999999999</v>
       </c>
       <c r="F23" s="2">
-        <v>17.5</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="G23" s="2">
         <v>8.75</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" s="80">
+      <c r="A24" s="1">
         <v>23</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="D24" s="29">
+        <v>148</v>
+      </c>
+      <c r="E24" s="29">
+        <v>41.041387999999998</v>
+      </c>
+      <c r="F24" s="2">
+        <v>41.3</v>
+      </c>
+      <c r="G24" s="2">
+        <v>11.45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>24</v>
+      </c>
+      <c r="B25" s="2">
+        <v>56</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D24" s="25">
-        <v>162.6</v>
-      </c>
-      <c r="E24" s="25">
-        <v>49.652334000000003</v>
-      </c>
-      <c r="F24" s="2">
-        <v>49.1</v>
-      </c>
-      <c r="G24" s="2">
-        <v>15.05</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" s="80">
-        <v>24</v>
-      </c>
-      <c r="B25" s="7">
-        <v>56</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="20">
-        <v>67.2</v>
-      </c>
-      <c r="E25" s="20">
-        <v>33.592500000000001</v>
+      <c r="D25" s="26">
+        <v>72.7</v>
+      </c>
+      <c r="E25" s="26">
+        <v>36.311250000000001</v>
       </c>
       <c r="F25" s="2">
         <v>20.3</v>
@@ -6372,801 +6361,801 @@
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" s="80">
+      <c r="A26" s="1">
         <v>25</v>
       </c>
-      <c r="B26" s="7">
+      <c r="B26" s="2">
         <v>57</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="26">
+        <v>32</v>
+      </c>
+      <c r="E26" s="26">
+        <v>15.950153999999999</v>
+      </c>
+      <c r="F26" s="2">
+        <v>8.9</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4.45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>26</v>
+      </c>
+      <c r="B27" s="2">
+        <v>58</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="20">
-        <v>119.8</v>
-      </c>
-      <c r="E26" s="20">
-        <v>59.753644000000001</v>
-      </c>
-      <c r="F26" s="2">
-        <v>36.200000000000003</v>
-      </c>
-      <c r="G26" s="2">
-        <v>18.05</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="80">
-        <v>26</v>
-      </c>
-      <c r="B27" s="7">
-        <v>58</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="D27" s="26">
+        <v>50</v>
+      </c>
+      <c r="E27" s="26">
+        <v>25.004999999999999</v>
+      </c>
+      <c r="F27" s="2">
+        <v>14</v>
+      </c>
+      <c r="G27" s="2">
+        <v>6.95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>27</v>
+      </c>
+      <c r="B28" s="2">
+        <v>59</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D27" s="20">
-        <v>52.3</v>
-      </c>
-      <c r="E27" s="20">
-        <v>26.19875</v>
-      </c>
-      <c r="F27" s="2">
-        <v>15.8</v>
-      </c>
-      <c r="G27" s="2">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" s="80">
-        <v>27</v>
-      </c>
-      <c r="B28" s="7">
-        <v>59</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="20">
-        <v>43.8</v>
-      </c>
-      <c r="E28" s="20">
-        <v>21.855</v>
+      <c r="D28" s="26">
+        <v>47.3</v>
+      </c>
+      <c r="E28" s="26">
+        <v>23.620625</v>
       </c>
       <c r="F28" s="2">
         <v>13.2</v>
       </c>
       <c r="G28" s="2">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" s="80">
+      <c r="A29" s="1">
         <v>28</v>
       </c>
-      <c r="B29" s="7">
+      <c r="B29" s="2">
         <v>6</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="20">
-        <v>236.8</v>
-      </c>
-      <c r="E29" s="20">
-        <v>45.783766999999997</v>
+      <c r="D29" s="26">
+        <v>240.2</v>
+      </c>
+      <c r="E29" s="26">
+        <v>40.604145000000003</v>
       </c>
       <c r="F29" s="2">
-        <v>71.599999999999994</v>
+        <v>67</v>
       </c>
       <c r="G29" s="2">
-        <v>13.85</v>
+        <v>11.35</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" s="80">
+      <c r="A30" s="1">
         <v>29</v>
       </c>
-      <c r="B30" s="7">
+      <c r="B30" s="2">
         <v>60</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" s="26">
+        <v>78.5</v>
+      </c>
+      <c r="E30" s="26">
+        <v>39.075031000000003</v>
+      </c>
+      <c r="F30" s="2">
+        <v>21.9</v>
+      </c>
+      <c r="G30" s="2">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>30</v>
+      </c>
+      <c r="B31" s="2">
+        <v>61</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D30" s="20">
-        <v>104.3</v>
-      </c>
-      <c r="E30" s="20">
-        <v>52.012507999999997</v>
-      </c>
-      <c r="F30" s="2">
-        <v>31.5</v>
-      </c>
-      <c r="G30" s="2">
-        <v>15.75</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" s="80">
-        <v>30</v>
-      </c>
-      <c r="B31" s="7">
-        <v>61</v>
-      </c>
-      <c r="C31" s="10" t="s">
+      <c r="D31" s="26">
+        <v>66.8</v>
+      </c>
+      <c r="E31" s="26">
+        <v>33.283368000000003</v>
+      </c>
+      <c r="F31" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="G31" s="2">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2">
+        <v>62</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D31" s="20">
-        <v>61.1</v>
-      </c>
-      <c r="E31" s="20">
-        <v>30.420275</v>
-      </c>
-      <c r="F31" s="2">
-        <v>18.5</v>
-      </c>
-      <c r="G31" s="2">
-        <v>9.1999999999999993</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" s="80">
+      <c r="D32" s="26">
+        <v>31.3</v>
+      </c>
+      <c r="E32" s="26">
+        <v>15.605</v>
+      </c>
+      <c r="F32" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="G32" s="2">
+        <v>4.3499999999999996</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>32</v>
+      </c>
+      <c r="B33" s="2">
+        <v>63</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D33" s="26">
+        <v>35.200000000000003</v>
+      </c>
+      <c r="E33" s="26">
+        <v>17.561250000000001</v>
+      </c>
+      <c r="F33" s="2">
+        <v>9.8000000000000007</v>
+      </c>
+      <c r="G33" s="2">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>33</v>
+      </c>
+      <c r="B34" s="2">
+        <v>64</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="26">
+        <v>34</v>
+      </c>
+      <c r="E34" s="26">
+        <v>16.989374999999999</v>
+      </c>
+      <c r="F34" s="2">
+        <v>9.5</v>
+      </c>
+      <c r="G34" s="2">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2">
+        <v>65</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D35" s="26">
+        <v>57.8</v>
+      </c>
+      <c r="E35" s="26">
+        <v>28.9175</v>
+      </c>
+      <c r="F35" s="2">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="G35" s="2">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="D36" s="29">
+        <v>115.9</v>
+      </c>
+      <c r="E36" s="29">
+        <v>28.098875</v>
+      </c>
+      <c r="F36" s="2">
+        <v>32.299999999999997</v>
+      </c>
+      <c r="G36" s="2">
+        <v>7.85</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2">
+        <v>66</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" s="26">
+        <v>71</v>
+      </c>
+      <c r="E37" s="26">
+        <v>35.318427</v>
+      </c>
+      <c r="F37" s="2">
+        <v>19.8</v>
+      </c>
+      <c r="G37" s="2">
+        <v>9.85</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2">
+        <v>67</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D38" s="26">
+        <v>42.4</v>
+      </c>
+      <c r="E38" s="26">
+        <v>21.129289</v>
+      </c>
+      <c r="F38" s="2">
+        <v>11.8</v>
+      </c>
+      <c r="G38" s="2">
+        <v>5.9</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2">
+        <v>68</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D39" s="26">
+        <v>38.299999999999997</v>
+      </c>
+      <c r="E39" s="26">
+        <v>19.13625</v>
+      </c>
+      <c r="F39" s="2">
+        <v>10.7</v>
+      </c>
+      <c r="G39" s="2">
+        <v>5.35</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2">
+        <v>69</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D40" s="26">
+        <v>51.6</v>
+      </c>
+      <c r="E40" s="26">
+        <v>25.767499999999998</v>
+      </c>
+      <c r="F40" s="2">
+        <v>14.4</v>
+      </c>
+      <c r="G40" s="2">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>40</v>
+      </c>
+      <c r="B41" s="2">
+        <v>7</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="26">
+        <v>2101.8000000000002</v>
+      </c>
+      <c r="E41" s="26">
+        <v>691.55091100000004</v>
+      </c>
+      <c r="F41" s="2">
+        <v>586.5</v>
+      </c>
+      <c r="G41" s="2">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>41</v>
+      </c>
+      <c r="B42" s="2">
+        <v>70</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="26">
+        <v>36.700000000000003</v>
+      </c>
+      <c r="E42" s="26">
+        <v>18.373750000000001</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G42" s="2">
+        <v>5.15</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>42</v>
+      </c>
+      <c r="B43" s="2">
+        <v>73</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D43" s="26">
+        <v>22</v>
+      </c>
+      <c r="E43" s="26">
+        <v>7.5323659999999997</v>
+      </c>
+      <c r="F43" s="2">
+        <v>6.2</v>
+      </c>
+      <c r="G43" s="2">
+        <v>2.0499999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2">
+        <v>75</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="26">
+        <v>97.5</v>
+      </c>
+      <c r="E44" s="26">
+        <v>7.569801</v>
+      </c>
+      <c r="F44" s="2">
+        <v>27.2</v>
+      </c>
+      <c r="G44" s="2">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>44</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="D45" s="29">
+        <v>78.7</v>
+      </c>
+      <c r="E45" s="29">
+        <v>8.9940320000000007</v>
+      </c>
+      <c r="F45" s="2">
+        <v>22</v>
+      </c>
+      <c r="G45" s="2">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>45</v>
+      </c>
+      <c r="B46" s="2">
+        <v>79</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D46" s="26">
+        <v>53.9</v>
+      </c>
+      <c r="E46" s="26">
+        <v>9.3371670000000009</v>
+      </c>
+      <c r="F46" s="2">
+        <v>15</v>
+      </c>
+      <c r="G46" s="2">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>46</v>
+      </c>
+      <c r="B47" s="2">
+        <v>8</v>
+      </c>
+      <c r="C47" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" s="29">
+        <v>35.4</v>
+      </c>
+      <c r="E47" s="29">
+        <v>5.8233610000000002</v>
+      </c>
+      <c r="F47" s="2">
+        <v>9.9</v>
+      </c>
+      <c r="G47" s="2">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>47</v>
+      </c>
+      <c r="B48" s="2">
+        <v>81</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="D48" s="26">
+        <v>66.900000000000006</v>
+      </c>
+      <c r="E48" s="26">
+        <v>5.9661249999999999</v>
+      </c>
+      <c r="F48" s="2">
+        <v>18.7</v>
+      </c>
+      <c r="G48" s="2">
+        <v>1.65</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>48</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D49" s="29">
+        <v>14.5</v>
+      </c>
+      <c r="E49" s="29">
+        <v>7.2546330000000001</v>
+      </c>
+      <c r="F49" s="2">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G49" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2">
+        <v>83</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B32" s="7">
-        <v>62</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="20">
-        <v>22.9</v>
-      </c>
-      <c r="E32" s="20">
-        <v>11.406563</v>
-      </c>
-      <c r="F32" s="2">
-        <v>6.9</v>
-      </c>
-      <c r="G32" s="2">
-        <v>3.45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" s="80">
+      <c r="D50" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E50" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>50</v>
+      </c>
+      <c r="B51" s="2">
+        <v>84</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B33" s="7">
-        <v>63</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33" s="20">
-        <v>26.2</v>
-      </c>
-      <c r="E33" s="20">
-        <v>13.076874999999999</v>
-      </c>
-      <c r="F33" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="G33" s="2">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" s="80">
+      <c r="D51" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E51" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2">
+        <v>85</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B34" s="7">
-        <v>64</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D34" s="20">
-        <v>25.4</v>
-      </c>
-      <c r="E34" s="20">
-        <v>12.695625</v>
-      </c>
-      <c r="F34" s="2">
-        <v>7.7</v>
-      </c>
-      <c r="G34" s="2">
-        <v>3.85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" s="80">
-        <v>34</v>
-      </c>
-      <c r="B35" s="7">
-        <v>65</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D35" s="20">
-        <v>57.8</v>
-      </c>
-      <c r="E35" s="20">
-        <v>28.9175</v>
-      </c>
-      <c r="F35" s="2">
-        <v>17.5</v>
-      </c>
-      <c r="G35" s="2">
-        <v>8.75</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A36" s="80">
+      <c r="D52" s="26">
+        <v>58.6</v>
+      </c>
+      <c r="E52" s="26">
+        <v>22.638100999999999</v>
+      </c>
+      <c r="F52" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="G52" s="2">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>52</v>
+      </c>
+      <c r="B53" s="2">
+        <v>86</v>
+      </c>
+      <c r="C53" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B36" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="D36" s="20">
-        <v>96</v>
-      </c>
-      <c r="E36" s="20">
-        <v>37.812362999999998</v>
-      </c>
-      <c r="F36" s="2">
-        <v>29</v>
-      </c>
-      <c r="G36" s="2">
-        <v>11.45</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A37" s="80">
+      <c r="D53" s="26">
+        <v>58.6</v>
+      </c>
+      <c r="E53" s="26">
+        <v>22.638100999999999</v>
+      </c>
+      <c r="F53" s="2">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="G53" s="2">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2">
+        <v>87</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="7">
-        <v>66</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="20">
-        <v>70.599999999999994</v>
-      </c>
-      <c r="E37" s="20">
-        <v>35.056998</v>
-      </c>
-      <c r="F37" s="2">
-        <v>21.3</v>
-      </c>
-      <c r="G37" s="2">
-        <v>10.6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A38" s="80">
-        <v>37</v>
-      </c>
-      <c r="B38" s="7">
-        <v>67</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="D38" s="20">
-        <v>34.9</v>
-      </c>
-      <c r="E38" s="20">
-        <v>17.400437</v>
-      </c>
-      <c r="F38" s="2">
-        <v>10.5</v>
-      </c>
-      <c r="G38" s="2">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="80">
-        <v>38</v>
-      </c>
-      <c r="B39" s="7">
-        <v>68</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D39" s="20">
-        <v>38.700000000000003</v>
-      </c>
-      <c r="E39" s="20">
-        <v>19.326875000000001</v>
-      </c>
-      <c r="F39" s="2">
-        <v>11.7</v>
-      </c>
-      <c r="G39" s="2">
-        <v>5.85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="80">
+      <c r="D54" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E54" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>54</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C55" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="D55" s="29">
+        <v>11.4</v>
+      </c>
+      <c r="E55" s="29">
+        <v>1.663799</v>
+      </c>
+      <c r="F55" s="2">
+        <v>3.2</v>
+      </c>
+      <c r="G55" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>55</v>
+      </c>
+      <c r="B56" s="2">
+        <v>89</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="7">
-        <v>69</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D40" s="20">
-        <v>50.8</v>
-      </c>
-      <c r="E40" s="20">
-        <v>25.38625</v>
-      </c>
-      <c r="F40" s="2">
-        <v>15.4</v>
-      </c>
-      <c r="G40" s="2">
-        <v>7.65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="80">
+      <c r="D56" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>56</v>
+      </c>
+      <c r="B57" s="2">
+        <v>9</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D57" s="26">
+        <v>144.19999999999999</v>
+      </c>
+      <c r="E57" s="26">
+        <v>33.05977</v>
+      </c>
+      <c r="F57" s="2">
+        <v>40.200000000000003</v>
+      </c>
+      <c r="G57" s="2">
+        <v>9.25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>57</v>
+      </c>
+      <c r="B58" s="2">
+        <v>91</v>
+      </c>
+      <c r="C58" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="7">
-        <v>7</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D41" s="20">
-        <v>6613.8</v>
-      </c>
-      <c r="E41" s="20">
-        <v>3306.8558290000001</v>
-      </c>
-      <c r="F41" s="2">
-        <v>1999.5</v>
-      </c>
-      <c r="G41" s="2">
-        <v>999.7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A42" s="80">
+      <c r="D58" s="26">
+        <v>3</v>
+      </c>
+      <c r="E58" s="26">
+        <v>1.508505</v>
+      </c>
+      <c r="F58" s="2">
+        <v>0.8</v>
+      </c>
+      <c r="G58" s="2">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>58</v>
+      </c>
+      <c r="B59" s="2">
+        <v>92</v>
+      </c>
+      <c r="C59" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="7">
-        <v>70</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="20">
-        <v>28.1</v>
-      </c>
-      <c r="E42" s="20">
-        <v>14.08</v>
-      </c>
-      <c r="F42" s="2">
-        <v>8.5</v>
-      </c>
-      <c r="G42" s="2">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A43" s="80">
+      <c r="D59" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E59" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>59</v>
+      </c>
+      <c r="B60" s="2">
+        <v>93</v>
+      </c>
+      <c r="C60" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="7">
-        <v>73</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>23</v>
-      </c>
-      <c r="D43" s="20">
-        <v>26</v>
-      </c>
-      <c r="E43" s="20">
-        <v>8.8778919999999992</v>
-      </c>
-      <c r="F43" s="2">
-        <v>7.9</v>
-      </c>
-      <c r="G43" s="2">
-        <v>2.65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A44" s="80">
-        <v>43</v>
-      </c>
-      <c r="B44" s="7">
-        <v>75</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="D44" s="20">
-        <v>96.2</v>
-      </c>
-      <c r="E44" s="20">
-        <v>8.898301</v>
-      </c>
-      <c r="F44" s="2">
-        <v>29.1</v>
-      </c>
-      <c r="G44" s="2">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="80">
-        <v>44</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C45" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="D45" s="25">
-        <v>75.7</v>
-      </c>
-      <c r="E45" s="25">
-        <v>9.9753150000000002</v>
-      </c>
-      <c r="F45" s="2">
-        <v>22.9</v>
-      </c>
-      <c r="G45" s="2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A46" s="80">
-        <v>45</v>
-      </c>
-      <c r="B46" s="7">
-        <v>79</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="D46" s="20">
-        <v>45.8</v>
-      </c>
-      <c r="E46" s="20">
-        <v>13.832689999999999</v>
-      </c>
-      <c r="F46" s="2">
-        <v>13.8</v>
-      </c>
-      <c r="G46" s="2">
-        <v>4.2</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="80">
-        <v>46</v>
-      </c>
-      <c r="B47" s="7">
-        <v>8</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="D47" s="25">
-        <v>32.4</v>
-      </c>
-      <c r="E47" s="25">
-        <v>5.4698450000000003</v>
-      </c>
-      <c r="F47" s="2">
-        <v>9.8000000000000007</v>
-      </c>
-      <c r="G47" s="2">
-        <v>1.65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A48" s="80">
-        <v>47</v>
-      </c>
-      <c r="B48" s="7">
-        <v>81</v>
-      </c>
-      <c r="C48" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="D48" s="20">
-        <v>64.099999999999994</v>
-      </c>
-      <c r="E48" s="20">
-        <v>6.3913989999999998</v>
-      </c>
-      <c r="F48" s="2">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="G48" s="2">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A49" s="80">
-        <v>48</v>
-      </c>
-      <c r="B49" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C49" s="24" t="s">
-        <v>55</v>
-      </c>
-      <c r="D49" s="25">
-        <v>21.5</v>
-      </c>
-      <c r="E49" s="25">
-        <v>10.659886999999999</v>
-      </c>
-      <c r="F49" s="2">
-        <v>6.5</v>
-      </c>
-      <c r="G49" s="2">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A50" s="80">
-        <v>49</v>
-      </c>
-      <c r="B50" s="7">
-        <v>83</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A51" s="80">
-        <v>50</v>
-      </c>
-      <c r="B51" s="7">
-        <v>84</v>
-      </c>
-      <c r="C51" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A52" s="80">
-        <v>51</v>
-      </c>
-      <c r="B52" s="7">
-        <v>85</v>
-      </c>
-      <c r="C52" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="D52" s="20">
-        <v>66</v>
-      </c>
-      <c r="E52" s="20">
-        <v>26.388843000000001</v>
-      </c>
-      <c r="F52" s="2">
-        <v>20</v>
-      </c>
-      <c r="G52" s="2">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A53" s="80">
-        <v>52</v>
-      </c>
-      <c r="B53" s="7">
-        <v>86</v>
-      </c>
-      <c r="C53" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D53" s="20">
-        <v>66</v>
-      </c>
-      <c r="E53" s="20">
-        <v>26.388843000000001</v>
-      </c>
-      <c r="F53" s="2">
-        <v>20</v>
-      </c>
-      <c r="G53" s="2">
-        <v>7.95</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A54" s="80">
-        <v>53</v>
-      </c>
-      <c r="B54" s="7">
-        <v>87</v>
-      </c>
-      <c r="C54" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="D54" s="20">
-        <v>4647.8</v>
-      </c>
-      <c r="E54" s="20">
-        <v>1807.5099150000001</v>
-      </c>
-      <c r="F54" s="2">
-        <v>1405.1</v>
-      </c>
-      <c r="G54" s="2">
-        <v>546.45000000000005</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A55" s="80">
-        <v>54</v>
-      </c>
-      <c r="B55" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C55" s="24" t="s">
-        <v>57</v>
-      </c>
-      <c r="D55" s="25">
-        <v>11.6</v>
-      </c>
-      <c r="E55" s="25">
-        <v>1.6051949999999999</v>
-      </c>
-      <c r="F55" s="2">
-        <v>3.5</v>
-      </c>
-      <c r="G55" s="2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A56" s="80">
-        <v>55</v>
-      </c>
-      <c r="B56" s="7">
-        <v>89</v>
-      </c>
-      <c r="C56" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="D56" s="20">
-        <v>4591.7</v>
-      </c>
-      <c r="E56" s="20">
-        <v>1785.672286</v>
-      </c>
-      <c r="F56" s="2">
-        <v>1388.2</v>
-      </c>
-      <c r="G56" s="2">
-        <v>539.79999999999995</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A57" s="80">
-        <v>56</v>
-      </c>
-      <c r="B57" s="7">
-        <v>9</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>7</v>
-      </c>
-      <c r="D57" s="20">
-        <v>129.1</v>
-      </c>
-      <c r="E57" s="20">
-        <v>40.186065999999997</v>
-      </c>
-      <c r="F57" s="2">
-        <v>39</v>
-      </c>
-      <c r="G57" s="2">
-        <v>12.15</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A58" s="80">
-        <v>57</v>
-      </c>
-      <c r="B58" s="7">
-        <v>91</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="D58" s="20">
-        <v>2.9</v>
-      </c>
-      <c r="E58" s="20">
-        <v>1.4077869999999999</v>
-      </c>
-      <c r="F58" s="2">
-        <v>0.9</v>
-      </c>
-      <c r="G58" s="2">
-        <v>0.4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A59" s="80">
-        <v>58</v>
-      </c>
-      <c r="B59" s="7">
-        <v>92</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="D59" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E59" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A60" s="80">
-        <v>59</v>
-      </c>
-      <c r="B60" s="7">
-        <v>93</v>
-      </c>
-      <c r="C60" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D60" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="E60" s="22" t="s">
+      <c r="D60" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="E60" s="27" t="s">
         <v>34</v>
       </c>
       <c r="F60" s="3" t="s">
@@ -7178,6 +7167,10 @@
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="4"/>
+      <c r="B61"/>
+      <c r="C61"/>
+      <c r="D61" s="94"/>
+      <c r="E61" s="94"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -7196,10 +7189,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" t="s">
         <v>93</v>
-      </c>
-      <c r="B1" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
